--- a/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
+++ b/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BVS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\trans\BVS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B291C5C-0D68-4026-BF5B-12E51E7484B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FEC4C98-09EB-4A72-B928-46EF777001B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -45,8 +45,107 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Daniel O'Brien</author>
+    <author>tc={838D9E4A-FB93-4B31-99BC-34A5B3DDC0E3}</author>
+    <author>tc={741FCEA6-F177-4B34-877A-4D6E81B99010}</author>
+  </authors>
+  <commentList>
+    <comment ref="K16" authorId="0" shapeId="0" xr:uid="{5360E313-EC74-4D8F-BAE2-E743E264FB32}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Daniel O'Brien:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Where data is available, we take the total ev subsidy spend and divide by the total sales of EVs in the state</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{F5AC01E3-5D5B-4469-AC39-12AA7E3BADD7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Daniel O'Brien:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+BEV standard rebate reduced to 1500 on 1/1/25
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D28" authorId="1" shapeId="0" xr:uid="{838D9E4A-FB93-4B31-99BC-34A5B3DDC0E3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Adjust weighting for PA - only first 500 people get it</t>
+      </text>
+    </comment>
+    <comment ref="D48" authorId="2" shapeId="0" xr:uid="{741FCEA6-F177-4B34-877A-4D6E81B99010}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Adjust weighting for PA - only first 500 people get it</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="123">
   <si>
     <t>Sources:</t>
   </si>
@@ -87,9 +186,6 @@
     <t>It also omits states that do not offer a rebate but do exempt EVs from sales, use, or excise taxes.</t>
   </si>
   <si>
-    <t>State Rebates + Tax Credits Updated 8/11/2021</t>
-  </si>
-  <si>
     <t>TC</t>
   </si>
   <si>
@@ -120,9 +216,6 @@
     <t>LDV</t>
   </si>
   <si>
-    <t>Note: average of cars and truck subsidies, which are different</t>
-  </si>
-  <si>
     <t>CT</t>
   </si>
   <si>
@@ -133,9 +226,6 @@
   </si>
   <si>
     <t>NY</t>
-  </si>
-  <si>
-    <t>Subsidy goes up to 2000 based on battery</t>
   </si>
   <si>
     <t>TX</t>
@@ -168,16 +258,10 @@
     <t>VT</t>
   </si>
   <si>
-    <t>Note: Up to 4000</t>
-  </si>
-  <si>
     <t>Rest of country</t>
   </si>
   <si>
     <t>USA</t>
-  </si>
-  <si>
-    <t>Note: Pennsylvania offers a $1750 rebate, but only to the first 250 qualified applicants.</t>
   </si>
   <si>
     <t>Total Tax Credit (2012$)</t>
@@ -211,9 +295,6 @@
   </si>
   <si>
     <t>Calculations:</t>
-  </si>
-  <si>
-    <t>2022 $ to 2012 $</t>
   </si>
   <si>
     <t>Fraction of buses owned by private entities (see trans/FoVObE)</t>
@@ -288,9 +369,6 @@
     <t>Freight HDV (2012 $)</t>
   </si>
   <si>
-    <t>Psgr LDV (2012 $)</t>
-  </si>
-  <si>
     <t>Credit Amount (2012 $)</t>
   </si>
   <si>
@@ -300,16 +378,142 @@
     <t>AEO 2023</t>
   </si>
   <si>
-    <t>values from original IRA analysis</t>
-  </si>
-  <si>
     <t>Foreign Entities of Concern Multiplier</t>
   </si>
   <si>
     <t>BloombergNEF, MarkLines, Department of Energy</t>
   </si>
   <si>
-    <t>We assume a 56% cut in our original analysis to represent FEOC restrictions for the year 2024, based on BNEF data. We assume more restrictive guidance starting in 2025 will reduce the credit amount by 75%.</t>
+    <t>data 1</t>
+  </si>
+  <si>
+    <t>data 2</t>
+  </si>
+  <si>
+    <t>https://tax.colorado.gov/sites/tax/files/documents/ITT_Innovative_Motor_Vehicle_Credit_Feb_2024.pdf</t>
+  </si>
+  <si>
+    <t>https://portal.ct.gov/ceq/ar-23-gold/2023-ceq-annual-report-ebook/personal-impact---waste-diversion/transportation</t>
+  </si>
+  <si>
+    <t>https://data.delaware.gov/Energy-and-Environment/State-Rebates-for-Alternative-Fuel-Vehicles/8z8z-di7f/explore</t>
+  </si>
+  <si>
+    <t>https://www.nyserda.ny.gov/All-Programs/Drive-Clean-Rebate-For-Electric-Cars-Program/Rebate-Data/Rebate-Stats</t>
+  </si>
+  <si>
+    <t>https://www.nyserda.ny.gov/All-Programs/Drive-Clean-Rebate-For-Electric-Cars-Program/Rebate-Data/Map-of-EV-Registrations</t>
+  </si>
+  <si>
+    <t>https://cleanvehiclerebate.org/en/rebate-statistics</t>
+  </si>
+  <si>
+    <t>https://www.energy.ca.gov/data-reports/energy-almanac/zero-emission-vehicle-and-infrastructure-statistics-collection/new-zev</t>
+  </si>
+  <si>
+    <t>Note: value was previously 1500 but after digging I don’t believe LA has ever had a state tax credit</t>
+  </si>
+  <si>
+    <t>suspended all ev rebate programs starting in 2024</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>no longer funds program</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>Note; renewed on annual basis, only for first 500</t>
+  </si>
+  <si>
+    <t>RI</t>
+  </si>
+  <si>
+    <t>up to 4k if low income</t>
+  </si>
+  <si>
+    <t>https://evrebate.oregon.gov/rebate-statistics</t>
+  </si>
+  <si>
+    <t>https://www.oregon.gov/energy/Data-and-Reports/Pages/Oregon-Electric-Vehicle-Dashboard.aspx</t>
+  </si>
+  <si>
+    <t>up to 3.2k if low income</t>
+  </si>
+  <si>
+    <t>PHEV Subsidies</t>
+  </si>
+  <si>
+    <t>US average share of EVs leased vs purchased</t>
+  </si>
+  <si>
+    <t>https://www.experian.com/blogs/ask-experian/electric-vehicle-trends/</t>
+  </si>
+  <si>
+    <t>Inflation adjuster</t>
+  </si>
+  <si>
+    <t>Inflation Historical Data and Assumptions</t>
+  </si>
+  <si>
+    <t>2012............................................................................. .</t>
+  </si>
+  <si>
+    <t>2013............................................................................. .</t>
+  </si>
+  <si>
+    <t>2014............................................................................. .</t>
+  </si>
+  <si>
+    <t>2015............................................................................. .</t>
+  </si>
+  <si>
+    <t>2016............................................................................. .</t>
+  </si>
+  <si>
+    <t>2017............................................................................. .</t>
+  </si>
+  <si>
+    <t>2018............................................................................. .</t>
+  </si>
+  <si>
+    <t>2019............................................................................. .</t>
+  </si>
+  <si>
+    <t>2020............................................................................. .</t>
+  </si>
+  <si>
+    <t>2021............................................................................. .</t>
+  </si>
+  <si>
+    <t>2022............................................................................. .</t>
+  </si>
+  <si>
+    <t>2023............................................................................. .</t>
+  </si>
+  <si>
+    <t>2024............................................................................. .</t>
+  </si>
+  <si>
+    <t>Future inflation assumption:</t>
+  </si>
+  <si>
+    <t>These values come from our internal analysis of weighted 30D and 45W purchase and leasing credits. (ICCT spreadsheet)</t>
+  </si>
+  <si>
+    <t>State Rebates + Tax Credits Updated 1/30/25</t>
+  </si>
+  <si>
+    <t>Updated 2/11/25</t>
+  </si>
+  <si>
+    <t>Conversion to 2012$</t>
+  </si>
+  <si>
+    <t>Frgt LDV (2012 $)</t>
   </si>
 </sst>
 </file>
@@ -320,11 +524,11 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="m\-d"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="m\-d"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -450,8 +654,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -468,6 +685,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCFE2F3"/>
         <bgColor rgb="FFCFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -516,7 +751,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="33">
+  <cellStyleXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
@@ -590,8 +825,9 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -607,7 +843,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="38" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -629,11 +864,11 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="31" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="31" applyFont="1"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="31" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="31" applyFont="1"/>
@@ -648,13 +883,30 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="32" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="31" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="31" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="31" applyFont="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="31" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="12" fillId="4" borderId="0" xfId="31" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="31" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="31" applyFill="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="33" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="31" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="33">
+  <cellStyles count="34">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Body: normal cell 2" xfId="24" xr:uid="{18BAE46B-2E2B-4189-9E60-EEC8494BA028}"/>
     <cellStyle name="Body: normal cell 3" xfId="17" xr:uid="{46606A30-9DB6-4D96-9D39-18DB8C25C045}"/>
     <cellStyle name="Body: normal cell 4" xfId="9" xr:uid="{23D7D41B-0FA5-4B15-8ACE-D94C027772C4}"/>
+    <cellStyle name="Currency" xfId="33" builtinId="4"/>
     <cellStyle name="Currency 2" xfId="32" xr:uid="{C53AF8AC-2A66-4CBB-880E-1554F67B4888}"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="6" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Font: Calibri, 9pt regular 2" xfId="25" xr:uid="{97A6AFB7-D07D-4277-A8A5-6AA031407B07}"/>
@@ -745,6 +997,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Olivia Ashmoore" id="{810A4951-0CFA-4CDB-88D1-6340A66E89CD}" userId="S::olivia@energyinnovation.org::75aa6550-3462-4480-900f-0bd2e542e876" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1032,6 +1290,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D28" dT="2025-01-24T19:38:54.68" personId="{810A4951-0CFA-4CDB-88D1-6340A66E89CD}" id="{838D9E4A-FB93-4B31-99BC-34A5B3DDC0E3}">
+    <text>Adjust weighting for PA - only first 500 people get it</text>
+  </threadedComment>
+  <threadedComment ref="D48" dT="2025-01-24T19:38:54.68" personId="{810A4951-0CFA-4CDB-88D1-6340A66E89CD}" id="{741FCEA6-F177-4B34-877A-4D6E81B99010}">
+    <text>Adjust weighting for PA - only first 500 people get it</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
@@ -1049,13 +1318,13 @@
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>50</v>
+      <c r="B3" s="19" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1065,20 +1334,20 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B8" s="20" t="s">
-        <v>85</v>
+      <c r="B8" s="19" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -2008,44 +2277,44 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <f>'Commercial Vehicles'!B11</f>
-        <v>10121.162702145082</v>
+        <f>'Commercial Vehicles'!B10</f>
+        <v>9715.0710076103514</v>
       </c>
       <c r="E2">
-        <f>'Commercial Vehicles'!C11</f>
-        <v>10059.772494365814</v>
+        <f>'Commercial Vehicles'!C10</f>
+        <v>9379.5012804435319</v>
       </c>
       <c r="F2">
-        <f>'Commercial Vehicles'!D11</f>
-        <v>10050.763799597085</v>
+        <f>'Commercial Vehicles'!D10</f>
+        <v>9098.157067904207</v>
       </c>
       <c r="G2">
-        <f>'Commercial Vehicles'!E11</f>
-        <v>10127.428607069427</v>
+        <f>'Commercial Vehicles'!E10</f>
+        <v>8900.5394373583313</v>
       </c>
       <c r="H2">
-        <f>'Commercial Vehicles'!F11</f>
-        <v>10269.11524721545</v>
+        <f>'Commercial Vehicles'!F10</f>
+        <v>8762.1955571514172</v>
       </c>
       <c r="I2">
-        <f>'Commercial Vehicles'!G11</f>
-        <v>10350.781370900584</v>
+        <f>'Commercial Vehicles'!G10</f>
+        <v>8574.638599520662</v>
       </c>
       <c r="J2">
-        <f>'Commercial Vehicles'!H11</f>
-        <v>10353.674088089921</v>
+        <f>'Commercial Vehicles'!H10</f>
+        <v>8327.2183891071436</v>
       </c>
       <c r="K2">
-        <f>'Commercial Vehicles'!I11</f>
-        <v>10294.239800360298</v>
+        <f>'Commercial Vehicles'!I10</f>
+        <v>8038.2687173078502</v>
       </c>
       <c r="L2">
-        <f>'Commercial Vehicles'!J11</f>
-        <v>10251.903689786537</v>
+        <f>'Commercial Vehicles'!J10</f>
+        <v>7772.0490463949827</v>
       </c>
       <c r="M2">
-        <f>'Commercial Vehicles'!K11</f>
-        <v>10279.777009851599</v>
+        <f>'Commercial Vehicles'!K10</f>
+        <v>7566.1942040579743</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -2399,43 +2668,43 @@
       </c>
       <c r="D6">
         <f>D2</f>
-        <v>10121.162702145082</v>
+        <v>9715.0710076103514</v>
       </c>
       <c r="E6">
         <f t="shared" ref="E6:M6" si="0">E2</f>
-        <v>10059.772494365814</v>
+        <v>9379.5012804435319</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>10050.763799597085</v>
+        <v>9098.157067904207</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>10127.428607069427</v>
+        <v>8900.5394373583313</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>10269.11524721545</v>
+        <v>8762.1955571514172</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>10350.781370900584</v>
+        <v>8574.638599520662</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>10353.674088089921</v>
+        <v>8327.2183891071436</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>10294.239800360298</v>
+        <v>8038.2687173078502</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>10251.903689786537</v>
+        <v>7772.0490463949827</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>10279.777009851599</v>
+        <v>7566.1942040579743</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2599,43 +2868,43 @@
       </c>
       <c r="D8">
         <f>D2</f>
-        <v>10121.162702145082</v>
+        <v>9715.0710076103514</v>
       </c>
       <c r="E8">
         <f t="shared" ref="E8:M8" si="1">E2</f>
-        <v>10059.772494365814</v>
+        <v>9379.5012804435319</v>
       </c>
       <c r="F8">
         <f t="shared" si="1"/>
-        <v>10050.763799597085</v>
+        <v>9098.157067904207</v>
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>10127.428607069427</v>
+        <v>8900.5394373583313</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>10269.11524721545</v>
+        <v>8762.1955571514172</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>10350.781370900584</v>
+        <v>8574.638599520662</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>10353.674088089921</v>
+        <v>8327.2183891071436</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>10294.239800360298</v>
+        <v>8038.2687173078502</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>10251.903689786537</v>
+        <v>7772.0490463949827</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>10279.777009851599</v>
+        <v>7566.1942040579743</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2707,6 +2976,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.35">
@@ -2814,45 +3084,45 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="E2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="F2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="G2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="H2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="I2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="J2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="K2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="L2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
-      </c>
-      <c r="M2">
-        <f>'Commercial Vehicles'!$B$8</f>
-        <v>31400</v>
+      <c r="D2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!C14</f>
+        <v>30140.136920663466</v>
+      </c>
+      <c r="E2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!D14</f>
+        <v>29276.640239217821</v>
+      </c>
+      <c r="F2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!E14</f>
+        <v>28423.922562347398</v>
+      </c>
+      <c r="G2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!F14</f>
+        <v>27596.041322667374</v>
+      </c>
+      <c r="H2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!G14</f>
+        <v>26792.273128803277</v>
+      </c>
+      <c r="I2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!H14</f>
+        <v>26011.915659032311</v>
+      </c>
+      <c r="J2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!I14</f>
+        <v>25254.287047604183</v>
+      </c>
+      <c r="K2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!J14</f>
+        <v>24518.725288936101</v>
+      </c>
+      <c r="L2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!K14</f>
+        <v>23804.587659161265</v>
+      </c>
+      <c r="M2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!L14</f>
+        <v>23111.250154525496</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -3206,43 +3476,43 @@
       </c>
       <c r="D6">
         <f>D2</f>
-        <v>31400</v>
+        <v>30140.136920663466</v>
       </c>
       <c r="E6">
         <f t="shared" ref="E6:M6" si="0">E2</f>
-        <v>31400</v>
+        <v>29276.640239217821</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>28423.922562347398</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>27596.041322667374</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>26792.273128803277</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>26011.915659032311</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>25254.287047604183</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>24518.725288936101</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>23804.587659161265</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>31400</v>
+        <v>23111.250154525496</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3406,43 +3676,43 @@
       </c>
       <c r="D8">
         <f>D2</f>
-        <v>31400</v>
+        <v>30140.136920663466</v>
       </c>
       <c r="E8">
         <f t="shared" ref="E8:M8" si="1">E2</f>
-        <v>31400</v>
+        <v>29276.640239217821</v>
       </c>
       <c r="F8">
         <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>28423.922562347398</v>
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>27596.041322667374</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>26792.273128803277</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>26011.915659032311</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>25254.287047604183</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>24518.725288936101</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>23804.587659161265</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>31400</v>
+        <v>23111.250154525496</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -6609,271 +6879,166 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8A3CC6-8591-4A07-9E4B-1DE39D29E87F}">
-  <dimension ref="A1:AF59"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8A3CC6-8591-4A07-9E4B-1DE39D29E87F}">
+  <dimension ref="A1:AF107"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45.453125" customWidth="1"/>
     <col min="2" max="2" width="15.7265625" customWidth="1"/>
     <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="4" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="B3">
+      <c r="A3" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="B4">
         <v>2021</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>2022</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>2023</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>2024</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>2025</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>2026</v>
       </c>
-      <c r="H3">
+      <c r="H4">
         <v>2027</v>
       </c>
-      <c r="I3">
+      <c r="I4">
         <v>2028</v>
       </c>
-      <c r="J3">
+      <c r="J4">
         <v>2029</v>
       </c>
-      <c r="K3">
+      <c r="K4">
         <v>2030</v>
       </c>
-      <c r="L3">
+      <c r="L4">
         <v>2031</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <v>2032</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>2033</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>2034</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>2035</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>2036</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>2037</v>
       </c>
-      <c r="S3">
+      <c r="S4">
         <v>2038</v>
       </c>
-      <c r="T3">
+      <c r="T4">
         <v>2039</v>
       </c>
-      <c r="U3">
+      <c r="U4">
         <v>2040</v>
       </c>
-      <c r="V3">
+      <c r="V4">
         <v>2041</v>
       </c>
-      <c r="W3">
+      <c r="W4">
         <v>2042</v>
       </c>
-      <c r="X3">
+      <c r="X4">
         <v>2043</v>
       </c>
-      <c r="Y3">
+      <c r="Y4">
         <v>2044</v>
       </c>
-      <c r="Z3">
+      <c r="Z4">
         <v>2045</v>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <v>2046</v>
       </c>
-      <c r="AB3">
+      <c r="AB4">
         <v>2047</v>
       </c>
-      <c r="AC3">
+      <c r="AC4">
         <v>2048</v>
       </c>
-      <c r="AD3">
+      <c r="AD4">
         <v>2049</v>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <v>2050</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4">
-        <v>2435.88</v>
-      </c>
-      <c r="C4">
-        <v>1697.08</v>
-      </c>
-      <c r="D4">
-        <f>D9*(1-0.56)</f>
-        <v>1795.2747999999999</v>
-      </c>
-      <c r="E4">
-        <f t="shared" ref="E4:M4" si="0">E9*(1-0.56)</f>
-        <v>1761.5091999999997</v>
-      </c>
-      <c r="F4">
-        <f>F9*(1-0.75)</f>
-        <v>1102.7774999999999</v>
-      </c>
-      <c r="G4">
-        <f t="shared" ref="G4:M4" si="1">G9*(1-0.75)</f>
-        <v>1057.2825</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="1"/>
-        <v>1022.79</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="1"/>
-        <v>1024.8150000000001</v>
-      </c>
-      <c r="J4">
-        <f t="shared" si="1"/>
-        <v>1031.5474999999999</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="1"/>
-        <v>1089.8074999999999</v>
-      </c>
-      <c r="L4">
-        <f t="shared" si="1"/>
-        <v>1145.5925</v>
-      </c>
-      <c r="M4">
-        <f t="shared" si="1"/>
-        <v>1156.375</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5">
-        <v>6652.72</v>
-      </c>
-      <c r="C5">
-        <v>3617.05</v>
-      </c>
-      <c r="D5">
-        <f>D10*(1-0.56)</f>
-        <v>1795.2747999999999</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ref="E5:M5" si="2">E10*(1-0.56)</f>
-        <v>1761.5091999999997</v>
-      </c>
-      <c r="F5">
-        <f>F10*(1-0.75)</f>
-        <v>1102.7774999999999</v>
-      </c>
-      <c r="G5">
-        <f t="shared" ref="G5:M5" si="3">G10*(1-0.75)</f>
-        <v>1057.2825</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="3"/>
-        <v>1022.79</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="3"/>
-        <v>1024.8150000000001</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="3"/>
-        <v>1031.5474999999999</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="3"/>
-        <v>1089.8074999999999</v>
-      </c>
-      <c r="L5">
-        <f t="shared" si="3"/>
-        <v>1145.5925</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="3"/>
-        <v>1156.375</v>
+        <v>40</v>
+      </c>
+      <c r="B5" s="48">
+        <v>1646.4981124797289</v>
+      </c>
+      <c r="C5" s="48">
+        <v>1368.5857570401329</v>
+      </c>
+      <c r="D5" s="48">
+        <v>4795.9636566176632</v>
+      </c>
+      <c r="E5" s="48">
+        <v>3555.487701851609</v>
+      </c>
+      <c r="F5" s="48">
+        <v>3365.6876734116477</v>
+      </c>
+      <c r="G5" s="48">
+        <v>3118.2246810233032</v>
+      </c>
+      <c r="H5" s="48">
+        <v>2391.1775782482218</v>
+      </c>
+      <c r="I5" s="48">
+        <v>2424.5099210417061</v>
+      </c>
+      <c r="J5" s="48">
+        <v>2459.8873208312061</v>
+      </c>
+      <c r="K5" s="48">
+        <v>2497.1120748745493</v>
+      </c>
+      <c r="L5" s="48">
+        <v>2525.3972397122579</v>
+      </c>
+      <c r="M5" s="48">
+        <v>2552.5012628800359</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -6931,575 +7096,542 @@
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
+      <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="48">
+        <v>6652.7185168992282</v>
+      </c>
+      <c r="C6" s="48">
+        <v>3617.050692978903</v>
+      </c>
+      <c r="D6" s="48">
+        <v>3481.1983222883337</v>
+      </c>
+      <c r="E6" s="48">
+        <v>2846.5223385773729</v>
+      </c>
+      <c r="F6" s="48">
+        <v>2396.2166523302549</v>
+      </c>
+      <c r="G6" s="48">
+        <v>2262.2795944248228</v>
+      </c>
+      <c r="H6" s="48">
+        <v>2133.3803923218893</v>
+      </c>
+      <c r="I6" s="48">
+        <v>2079.4479927022094</v>
+      </c>
+      <c r="J6" s="48">
+        <v>2027.1389823455879</v>
+      </c>
+      <c r="K6" s="48">
+        <v>1976.3952724267306</v>
+      </c>
+      <c r="L6" s="48">
+        <v>1926.1484722201324</v>
+      </c>
+      <c r="M6" s="48">
+        <v>1877.1377242807455</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>84</v>
-      </c>
+      <c r="A7" s="5"/>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="B8">
-        <v>2021</v>
-      </c>
-      <c r="C8">
-        <v>2022</v>
-      </c>
-      <c r="D8">
-        <v>2023</v>
-      </c>
-      <c r="E8">
-        <v>2024</v>
-      </c>
-      <c r="F8">
-        <v>2025</v>
-      </c>
-      <c r="G8">
-        <v>2026</v>
-      </c>
-      <c r="H8">
-        <v>2027</v>
-      </c>
-      <c r="I8">
-        <v>2028</v>
-      </c>
-      <c r="J8">
-        <v>2029</v>
-      </c>
-      <c r="K8">
-        <v>2030</v>
-      </c>
-      <c r="L8">
-        <v>2031</v>
-      </c>
-      <c r="M8">
-        <v>2032</v>
-      </c>
-      <c r="N8">
-        <v>2033</v>
-      </c>
-      <c r="O8">
-        <v>2034</v>
-      </c>
-      <c r="P8">
-        <v>2035</v>
-      </c>
-      <c r="Q8">
-        <v>2036</v>
-      </c>
-      <c r="R8">
-        <v>2037</v>
-      </c>
-      <c r="S8">
-        <v>2038</v>
-      </c>
-      <c r="T8">
-        <v>2039</v>
-      </c>
-      <c r="U8">
-        <v>2040</v>
-      </c>
-      <c r="V8">
-        <v>2041</v>
-      </c>
-      <c r="W8">
-        <v>2042</v>
-      </c>
-      <c r="X8">
-        <v>2043</v>
-      </c>
-      <c r="Y8">
-        <v>2044</v>
-      </c>
-      <c r="Z8">
-        <v>2045</v>
-      </c>
-      <c r="AA8">
-        <v>2046</v>
-      </c>
-      <c r="AB8">
-        <v>2047</v>
-      </c>
-      <c r="AC8">
-        <v>2048</v>
-      </c>
-      <c r="AD8">
-        <v>2049</v>
-      </c>
-      <c r="AE8">
-        <v>2050</v>
-      </c>
+      <c r="A8" s="5"/>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9">
-        <v>2435.88</v>
-      </c>
-      <c r="C9">
-        <v>1697.08</v>
-      </c>
-      <c r="D9">
-        <v>4080.17</v>
-      </c>
-      <c r="E9">
-        <v>4003.43</v>
-      </c>
-      <c r="F9">
-        <v>4411.1099999999997</v>
-      </c>
-      <c r="G9">
-        <v>4229.13</v>
-      </c>
-      <c r="H9">
-        <v>4091.16</v>
-      </c>
-      <c r="I9">
-        <v>4099.26</v>
-      </c>
-      <c r="J9">
-        <v>4126.1899999999996</v>
-      </c>
-      <c r="K9">
-        <v>4359.2299999999996</v>
-      </c>
-      <c r="L9">
-        <v>4582.37</v>
-      </c>
-      <c r="M9">
-        <v>4625.5</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
+      <c r="A9" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10">
-        <v>6652.72</v>
-      </c>
-      <c r="C10">
-        <v>3617.05</v>
-      </c>
-      <c r="D10">
-        <v>4080.17</v>
-      </c>
-      <c r="E10">
-        <v>4003.43</v>
-      </c>
-      <c r="F10">
-        <v>4411.1099999999997</v>
-      </c>
-      <c r="G10">
-        <v>4229.13</v>
-      </c>
-      <c r="H10">
-        <v>4091.16</v>
-      </c>
-      <c r="I10">
-        <v>4099.26</v>
-      </c>
-      <c r="J10">
-        <v>4126.1899999999996</v>
-      </c>
-      <c r="K10">
-        <v>4359.2299999999996</v>
-      </c>
-      <c r="L10">
-        <v>4582.37</v>
-      </c>
-      <c r="M10">
-        <v>4625.5</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A11" s="5"/>
+      <c r="A11" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A12" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" s="7"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
-        <v>11</v>
+      <c r="A13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
-        <v>12</v>
+      <c r="A14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="7"/>
+      <c r="A15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="8"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="8">
+        <v>2020</v>
+      </c>
+      <c r="E16" s="8">
+        <f t="shared" ref="E16:J16" si="0">D16+1</f>
+        <v>2021</v>
+      </c>
+      <c r="F16" s="8">
+        <f t="shared" si="0"/>
+        <v>2022</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="0"/>
+        <v>2024</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="0"/>
+        <v>2025</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="0"/>
+        <v>2026</v>
+      </c>
+      <c r="K16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9" t="s">
-        <v>17</v>
+      <c r="A17" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="45">
+        <v>5.6849999999999996</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="36">
+        <f>2000*D76+4000*(1-D76)</f>
+        <v>3506.6</v>
+      </c>
+      <c r="E17" s="37">
+        <f>1500*E76+2500*(1-E76)</f>
+        <v>2190.8000000000002</v>
+      </c>
+      <c r="F17" s="37">
+        <f>1500*F76+2500*(1-F76)</f>
+        <v>2359</v>
+      </c>
+      <c r="G17" s="37">
+        <f>0.5*(1500*G76+2500*(1-G76))+0.5*(5000)</f>
+        <v>3641.35</v>
+      </c>
+      <c r="H17" s="37">
+        <v>5000</v>
+      </c>
+      <c r="I17" s="37">
+        <v>3500</v>
+      </c>
+      <c r="J17" s="37">
+        <f>I17</f>
+        <v>3500</v>
+      </c>
+      <c r="K17" s="36" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="8"/>
+      <c r="A18" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="45">
+        <v>3.5710000000000002</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="37">
+        <f>613500/(7880-5480)</f>
+        <v>255.625</v>
+      </c>
+      <c r="E18" s="37">
+        <f>1079750/(12513-7880)</f>
+        <v>233.05633498812864</v>
+      </c>
+      <c r="F18" s="37">
+        <f>1468250/(18509-12513)</f>
+        <v>244.87158105403603</v>
+      </c>
+      <c r="G18" s="37">
+        <f>7744000/(27709-18509)</f>
+        <v>841.73913043478262</v>
+      </c>
+      <c r="H18" s="37">
+        <f>11982750/(27146*27709/44313)</f>
+        <v>705.92888732943345</v>
+      </c>
+      <c r="I18" s="37">
+        <f>H18*1500/2250</f>
+        <v>470.61925821962228</v>
+      </c>
+      <c r="J18" s="37">
+        <f>I18</f>
+        <v>470.61925821962228</v>
+      </c>
+      <c r="K18" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="L18" t="s">
+        <v>82</v>
+      </c>
+      <c r="R18" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="B19" s="46">
+        <v>0.96799999999999997</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="8">
-        <v>2020</v>
-      </c>
-      <c r="E19" s="8">
-        <f t="shared" ref="E19:J19" si="4">D19+1</f>
-        <v>2021</v>
-      </c>
-      <c r="F19" s="8">
-        <f t="shared" si="4"/>
-        <v>2022</v>
-      </c>
-      <c r="G19" s="8">
-        <f t="shared" si="4"/>
-        <v>2023</v>
-      </c>
-      <c r="H19" s="8">
-        <f t="shared" si="4"/>
-        <v>2024</v>
-      </c>
-      <c r="I19" s="8">
-        <f t="shared" si="4"/>
-        <v>2025</v>
-      </c>
-      <c r="J19" s="8">
-        <f t="shared" si="4"/>
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="D19" s="38">
+        <f>852000/311</f>
+        <v>2739.5498392282957</v>
+      </c>
+      <c r="E19" s="38">
+        <f>2500</f>
+        <v>2500</v>
+      </c>
+      <c r="F19" s="38">
+        <f>2500</f>
+        <v>2500</v>
+      </c>
+      <c r="G19" s="38">
+        <f>2500</f>
+        <v>2500</v>
+      </c>
+      <c r="H19" s="38">
+        <f>2500</f>
+        <v>2500</v>
+      </c>
+      <c r="I19" s="38">
+        <f>2500</f>
+        <v>2500</v>
+      </c>
+      <c r="J19" s="38">
+        <f>2500</f>
+        <v>2500</v>
+      </c>
+      <c r="K19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="46">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="8">
-        <v>5.6849999999999996</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="8">
-        <v>4750</v>
-      </c>
-      <c r="E20" s="8">
-        <v>4750</v>
-      </c>
-      <c r="F20" s="8">
-        <v>3000</v>
-      </c>
-      <c r="G20" s="8">
-        <v>3000</v>
-      </c>
-      <c r="H20" s="8">
-        <v>2400</v>
-      </c>
-      <c r="I20" s="8">
-        <v>2400</v>
-      </c>
-      <c r="J20" s="8">
-        <v>2400</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="D20" s="38">
+        <f>17436700/10692</f>
+        <v>1630.8174335952115</v>
+      </c>
+      <c r="E20" s="38">
+        <f>18953100/20836</f>
+        <v>909.63236705701672</v>
+      </c>
+      <c r="F20" s="38">
+        <f>16215000/28241</f>
+        <v>574.16522077830109</v>
+      </c>
+      <c r="G20" s="38">
+        <f>26945500/48746</f>
+        <v>552.77356090756166</v>
+      </c>
+      <c r="H20" s="38">
+        <f>19221500/54664</f>
+        <v>351.62995755890529</v>
+      </c>
+      <c r="I20" s="38">
+        <f>H20</f>
+        <v>351.62995755890529</v>
+      </c>
+      <c r="J20" s="38">
+        <f>I20</f>
+        <v>351.62995755890529</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="M20" s="11"/>
+    </row>
+    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="8">
-        <v>3.5710000000000002</v>
+        <v>27</v>
+      </c>
+      <c r="B21" s="46">
+        <v>28.64</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" s="8">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="E21" s="8">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="F21" s="8">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="G21" s="8">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="H21" s="8">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="I21" s="8">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="J21" s="8">
-        <v>2250</v>
-      </c>
-      <c r="K21" s="8"/>
-      <c r="R21" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="10"/>
+      <c r="M21" s="11"/>
+    </row>
+    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="8">
-        <v>0.96799999999999997</v>
+        <v>29</v>
+      </c>
+      <c r="B22" s="46">
+        <v>39.35</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E22" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F22" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G22" s="8">
-        <v>2500</v>
+        <v>22</v>
+      </c>
+      <c r="D22" s="38">
+        <f>80255483/(100377+5569)</f>
+        <v>757.51310101372394</v>
+      </c>
+      <c r="E22" s="38">
+        <f>103494583/(152400+7866)</f>
+        <v>645.76755518949744</v>
+      </c>
+      <c r="F22" s="38">
+        <f>88529166/(256315+5761)</f>
+        <v>337.79959248462279</v>
+      </c>
+      <c r="G22" s="38">
+        <f>310602850/(371002+3666)</f>
+        <v>829.00821527325525</v>
       </c>
       <c r="H22" s="8">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="I22" s="8">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="J22" s="8">
-        <v>2500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="M22" s="11"/>
     </row>
     <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="8">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="11">
+        <v>30</v>
+      </c>
+      <c r="B23" s="46">
+        <v>4.665</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="13">
+        <v>0</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13">
+        <v>0</v>
+      </c>
+      <c r="G23" s="13">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
+        <v>0</v>
+      </c>
+      <c r="I23" s="13">
+        <v>0</v>
+      </c>
+      <c r="J23" s="13">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="L23" s="10"/>
+      <c r="M23" s="11"/>
+    </row>
+    <row r="24" spans="1:18" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="47">
+        <v>1.341</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="8">
         <v>2000</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E24" s="8">
         <v>2000</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F24" s="8">
         <v>2000</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G24" s="8">
         <v>2000</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H24" s="8">
         <v>2000</v>
       </c>
-      <c r="I23" s="11">
-        <v>2000</v>
-      </c>
-      <c r="J23" s="11">
-        <v>2000</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" s="10"/>
-      <c r="M23" s="12"/>
-    </row>
-    <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="8">
-        <v>28.64</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0</v>
-      </c>
-      <c r="F24" s="8">
-        <v>0</v>
-      </c>
-      <c r="G24" s="8">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8">
-        <v>0</v>
-      </c>
       <c r="I24" s="8">
         <v>0</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
       </c>
-      <c r="K24" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="R24" s="13"/>
+      <c r="K24" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="R24" s="12"/>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="8">
-        <v>39.35</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>23</v>
+      <c r="A25" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="47">
+        <v>5.7169999999999996</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="D25" s="8">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="E25" s="8">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="F25" s="8">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="G25" s="8">
         <v>2500</v>
@@ -7508,246 +7640,269 @@
         <v>2500</v>
       </c>
       <c r="I25" s="8">
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="47">
+        <v>6.0380000000000003</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="8">
         <v>2500</v>
       </c>
-      <c r="J25" s="8">
+      <c r="E26" s="8">
         <v>2500</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
+      <c r="F26" s="8">
+        <v>2500</v>
+      </c>
+      <c r="G26" s="8">
+        <v>3000</v>
+      </c>
+      <c r="H26" s="8">
+        <v>3000</v>
+      </c>
+      <c r="I26" s="8">
+        <v>3000</v>
+      </c>
+      <c r="J26" s="8">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="8">
-        <v>4.665</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="14">
+      <c r="B27" s="47">
+        <v>6.8730000000000002</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="8">
+        <v>2500</v>
+      </c>
+      <c r="E27" s="8">
+        <v>2500</v>
+      </c>
+      <c r="F27" s="8">
+        <v>2500</v>
+      </c>
+      <c r="G27" s="8">
+        <v>3500</v>
+      </c>
+      <c r="H27" s="8">
+        <v>3500</v>
+      </c>
+      <c r="I27" s="8">
+        <v>3500</v>
+      </c>
+      <c r="J27" s="8">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="47">
+        <f>500/10^6</f>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8">
+        <v>3000</v>
+      </c>
+      <c r="H28" s="8">
+        <v>3000</v>
+      </c>
+      <c r="I28" s="8">
+        <v>3000</v>
+      </c>
+      <c r="J28" s="8">
+        <v>3000</v>
+      </c>
+      <c r="K28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="47">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8">
         <v>1500</v>
       </c>
-      <c r="E26" s="14">
+      <c r="G29" s="8">
         <v>1500</v>
       </c>
-      <c r="F26" s="14">
+      <c r="H29" s="8">
         <v>1500</v>
       </c>
-      <c r="G26" s="14">
+      <c r="I29" s="8">
         <v>1500</v>
       </c>
-      <c r="H26" s="14">
+      <c r="J29" s="8">
         <v>1500</v>
       </c>
-      <c r="I26" s="14">
-        <v>1500</v>
-      </c>
-      <c r="J26" s="14">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
+    </row>
+    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="8">
-        <v>1.341</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="8">
+      <c r="B30" s="47">
+        <v>8.8849999999999998</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="8">
         <v>2000</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E30" s="8">
         <v>2000</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F30" s="8">
         <v>2000</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G30" s="8">
         <v>2000</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H30" s="8">
         <v>2000</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I30" s="8">
         <v>2000</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J30" s="8">
         <v>2000</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+      <c r="K30" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="8">
-        <v>6.0380000000000003</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="I28" s="8">
-        <v>2500</v>
-      </c>
-      <c r="J28" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
+      <c r="B31" s="47">
+        <v>4.1760000000000002</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="38">
+        <f>9294500/3753</f>
+        <v>2476.5520916600053</v>
+      </c>
+      <c r="E31" s="38">
+        <f>14303500/7764</f>
+        <v>1842.284904688305</v>
+      </c>
+      <c r="F31" s="38">
+        <f>19442500/12379</f>
+        <v>1570.6034413118991</v>
+      </c>
+      <c r="G31" s="38">
+        <f>13295000/19790</f>
+        <v>671.80394138453767</v>
+      </c>
+      <c r="H31" s="38">
+        <f>G31</f>
+        <v>671.80394138453767</v>
+      </c>
+      <c r="I31" s="38">
+        <f>H31</f>
+        <v>671.80394138453767</v>
+      </c>
+      <c r="J31" s="38">
+        <f>I31</f>
+        <v>671.80394138453767</v>
+      </c>
+      <c r="K31" t="s">
+        <v>96</v>
+      </c>
+      <c r="L31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="8">
-        <v>6.8730000000000002</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="I29" s="8">
-        <v>2500</v>
-      </c>
-      <c r="J29" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
+      <c r="B32" s="47">
+        <v>0.624</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="39">
+        <v>2200</v>
+      </c>
+      <c r="E32" s="39">
+        <v>2200</v>
+      </c>
+      <c r="F32" s="39">
+        <v>2200</v>
+      </c>
+      <c r="G32" s="39">
+        <v>2200</v>
+      </c>
+      <c r="H32" s="39">
+        <v>2200</v>
+      </c>
+      <c r="I32" s="39">
+        <v>2200</v>
+      </c>
+      <c r="J32" s="39">
+        <v>2200</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="8">
-        <v>8.8849999999999998</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="E30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="F30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="G30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="H30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="I30" s="8">
-        <v>5000</v>
-      </c>
-      <c r="J30" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="8">
-        <v>4.1760000000000002</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="E31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="F31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="G31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="I31" s="8">
-        <v>2500</v>
-      </c>
-      <c r="J31" s="8">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="8">
-        <v>0.624</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="E32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="F32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="G32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="H32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="I32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="J32" s="8">
-        <v>4000</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="8">
-        <f>B34-SUM(B20:B32)</f>
-        <v>210.304</v>
+      <c r="B33" s="46">
+        <f>B34-SUM(B17:B32)</f>
+        <v>203.49250000000001</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8">
@@ -7773,635 +7928,2086 @@
       </c>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B34" s="8">
         <v>329.5</v>
       </c>
     </row>
-    <row r="35" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="7"/>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A36" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A37" s="5"/>
-    </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38">
+    </row>
+    <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="8">
+        <v>2020</v>
+      </c>
+      <c r="E36" s="8">
+        <f t="shared" ref="E36:J36" si="1">D36+1</f>
+        <v>2021</v>
+      </c>
+      <c r="F36" s="8">
+        <f t="shared" si="1"/>
+        <v>2022</v>
+      </c>
+      <c r="G36" s="8">
+        <f t="shared" si="1"/>
+        <v>2023</v>
+      </c>
+      <c r="H36" s="8">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="I36" s="8">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="J36" s="8">
+        <f t="shared" si="1"/>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="36">
+        <v>5.6849999999999996</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="37">
+        <f>D17</f>
+        <v>3506.6</v>
+      </c>
+      <c r="E37" s="37">
+        <f t="shared" ref="E37:J37" si="2">E17</f>
+        <v>2190.8000000000002</v>
+      </c>
+      <c r="F37" s="37">
+        <f t="shared" si="2"/>
+        <v>2359</v>
+      </c>
+      <c r="G37" s="37">
+        <f t="shared" si="2"/>
+        <v>3641.35</v>
+      </c>
+      <c r="H37" s="37">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="I37" s="37">
+        <f t="shared" si="2"/>
+        <v>3500</v>
+      </c>
+      <c r="J37" s="37">
+        <f t="shared" si="2"/>
+        <v>3500</v>
+      </c>
+      <c r="L37"/>
+    </row>
+    <row r="38" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="36">
+        <v>3.5710000000000002</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" s="37">
+        <f>128000/255</f>
+        <v>501.96078431372547</v>
+      </c>
+      <c r="E38" s="37">
+        <f>537750/(8827-5893)</f>
+        <v>183.28220858895705</v>
+      </c>
+      <c r="F38" s="37">
+        <f>412000/(11615-8827)</f>
+        <v>147.77618364418939</v>
+      </c>
+      <c r="G38" s="37">
+        <f>512500/(16517-11615)</f>
+        <v>104.54916360669115</v>
+      </c>
+      <c r="H38" s="37">
+        <f>685000/(27146*16517/44313)</f>
+        <v>67.69938302941182</v>
+      </c>
+      <c r="I38" s="37">
+        <f>H38</f>
+        <v>67.69938302941182</v>
+      </c>
+      <c r="J38" s="37">
+        <f t="shared" ref="J38" si="3">I38</f>
+        <v>67.69938302941182</v>
+      </c>
+      <c r="L38"/>
+    </row>
+    <row r="39" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="8">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="38">
+        <f>104500/97</f>
+        <v>1077.319587628866</v>
+      </c>
+      <c r="E39" s="38">
+        <v>1000</v>
+      </c>
+      <c r="F39" s="38">
+        <v>1000</v>
+      </c>
+      <c r="G39" s="38">
+        <v>1000</v>
+      </c>
+      <c r="H39" s="38">
+        <v>1000</v>
+      </c>
+      <c r="I39" s="38">
+        <v>1000</v>
+      </c>
+      <c r="J39" s="38">
+        <v>1000</v>
+      </c>
+      <c r="L39"/>
+    </row>
+    <row r="40" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="8">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="38">
+        <f>4684500/6464</f>
+        <v>724.7060643564356</v>
+      </c>
+      <c r="E40" s="38">
+        <f>9996000/14360</f>
+        <v>696.10027855153203</v>
+      </c>
+      <c r="F40" s="38">
+        <f>5049700/14312</f>
+        <v>352.82979318054777</v>
+      </c>
+      <c r="G40" s="38">
+        <f>8627000/30164</f>
+        <v>286.00318260177693</v>
+      </c>
+      <c r="H40" s="38">
+        <f>7694000/35557</f>
+        <v>216.38495936102595</v>
+      </c>
+      <c r="I40" s="38">
+        <f>H40</f>
+        <v>216.38495936102595</v>
+      </c>
+      <c r="J40" s="38">
+        <f>I40</f>
+        <v>216.38495936102595</v>
+      </c>
+      <c r="L40"/>
+    </row>
+    <row r="41" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="8">
+        <v>28.64</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="8">
+        <v>2500</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8">
+        <v>0</v>
+      </c>
+      <c r="G41" s="8">
+        <v>0</v>
+      </c>
+      <c r="H41" s="8">
+        <v>0</v>
+      </c>
+      <c r="I41" s="8">
+        <v>0</v>
+      </c>
+      <c r="J41" s="8">
+        <v>0</v>
+      </c>
+      <c r="L41"/>
+    </row>
+    <row r="42" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" s="8">
+        <v>39.35</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="38">
+        <f>12007419/38153</f>
+        <v>314.71755825229997</v>
+      </c>
+      <c r="E42" s="38">
+        <f>10067604/53090</f>
+        <v>189.6327745338105</v>
+      </c>
+      <c r="F42" s="38">
+        <f>3681500/(43689)</f>
+        <v>84.266062395568682</v>
+      </c>
+      <c r="G42" s="38">
+        <f>8757316/(63496)</f>
+        <v>137.9191760110873</v>
+      </c>
+      <c r="H42" s="8">
+        <v>0</v>
+      </c>
+      <c r="I42" s="8">
+        <v>0</v>
+      </c>
+      <c r="J42" s="8">
+        <v>0</v>
+      </c>
+      <c r="L42"/>
+    </row>
+    <row r="43" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" s="8">
+        <v>4.665</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="13">
+        <v>0</v>
+      </c>
+      <c r="E43" s="13">
+        <v>0</v>
+      </c>
+      <c r="F43" s="13">
+        <v>0</v>
+      </c>
+      <c r="G43" s="13">
+        <v>0</v>
+      </c>
+      <c r="H43" s="13">
+        <v>0</v>
+      </c>
+      <c r="I43" s="13">
+        <v>0</v>
+      </c>
+      <c r="J43" s="13">
+        <v>0</v>
+      </c>
+      <c r="L43"/>
+    </row>
+    <row r="44" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="7">
+        <v>1.341</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="8">
+        <v>1000</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1000</v>
+      </c>
+      <c r="F44" s="8">
+        <v>1000</v>
+      </c>
+      <c r="G44" s="8">
+        <v>1000</v>
+      </c>
+      <c r="H44" s="8">
+        <v>1000</v>
+      </c>
+      <c r="I44" s="8">
+        <v>0</v>
+      </c>
+      <c r="J44" s="8">
+        <v>0</v>
+      </c>
+      <c r="L44"/>
+    </row>
+    <row r="45" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" s="7">
+        <v>5.7169999999999996</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="8">
+        <v>0</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8">
+        <v>0</v>
+      </c>
+      <c r="G45" s="8">
+        <v>2500</v>
+      </c>
+      <c r="H45" s="8">
+        <v>2500</v>
+      </c>
+      <c r="I45" s="8">
+        <v>0</v>
+      </c>
+      <c r="J45" s="8">
+        <v>0</v>
+      </c>
+      <c r="L45"/>
+    </row>
+    <row r="46" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B46" s="7">
+        <v>6.0380000000000003</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="8">
+        <v>2500</v>
+      </c>
+      <c r="E46" s="8">
+        <v>2500</v>
+      </c>
+      <c r="F46" s="8">
+        <v>2500</v>
+      </c>
+      <c r="G46" s="8">
+        <v>3000</v>
+      </c>
+      <c r="H46" s="8">
+        <v>3000</v>
+      </c>
+      <c r="I46" s="8">
+        <v>3000</v>
+      </c>
+      <c r="J46" s="8">
+        <v>3000</v>
+      </c>
+      <c r="L46"/>
+    </row>
+    <row r="47" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B47" s="7">
+        <v>6.8730000000000002</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" s="8">
+        <v>2500</v>
+      </c>
+      <c r="E47" s="8">
+        <v>2500</v>
+      </c>
+      <c r="F47" s="8">
+        <v>2500</v>
+      </c>
+      <c r="G47" s="8">
+        <f>G27*0.5</f>
+        <v>1750</v>
+      </c>
+      <c r="H47" s="8">
+        <v>0</v>
+      </c>
+      <c r="I47" s="8">
+        <v>0</v>
+      </c>
+      <c r="J47" s="8">
+        <v>0</v>
+      </c>
+      <c r="L47"/>
+    </row>
+    <row r="48" spans="1:12" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="7">
+        <f>500/10^6</f>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" s="8">
+        <v>0</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0</v>
+      </c>
+      <c r="F48" s="8">
+        <v>0</v>
+      </c>
+      <c r="G48" s="8">
+        <v>1500</v>
+      </c>
+      <c r="H48" s="8">
+        <v>1500</v>
+      </c>
+      <c r="I48" s="8">
+        <v>1500</v>
+      </c>
+      <c r="J48" s="8">
+        <v>1500</v>
+      </c>
+      <c r="L48"/>
+    </row>
+    <row r="49" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="7">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" s="8">
+        <v>0</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8">
+        <v>1000</v>
+      </c>
+      <c r="G49" s="8">
+        <v>1000</v>
+      </c>
+      <c r="H49" s="8">
+        <v>1000</v>
+      </c>
+      <c r="I49" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J49" s="8">
+        <v>1000</v>
+      </c>
+      <c r="L49"/>
+    </row>
+    <row r="50" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="7">
+        <v>8.8849999999999998</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="8">
+        <v>2000</v>
+      </c>
+      <c r="E50" s="8">
+        <v>2000</v>
+      </c>
+      <c r="F50" s="8">
+        <v>2000</v>
+      </c>
+      <c r="G50" s="8">
+        <v>0</v>
+      </c>
+      <c r="H50" s="8">
+        <v>0</v>
+      </c>
+      <c r="I50" s="8">
+        <v>0</v>
+      </c>
+      <c r="J50" s="8">
+        <v>0</v>
+      </c>
+      <c r="L50"/>
+    </row>
+    <row r="51" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="7">
+        <v>4.1760000000000002</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="8">
+        <f>1843000/1494</f>
+        <v>1233.6010709504685</v>
+      </c>
+      <c r="E51" s="8">
+        <f>4828500/4476</f>
+        <v>1078.7533512064342</v>
+      </c>
+      <c r="F51" s="8">
+        <f>5495500/4897</f>
+        <v>1122.217684296508</v>
+      </c>
+      <c r="G51" s="38">
+        <f>2876000/6464</f>
+        <v>444.92574257425741</v>
+      </c>
+      <c r="H51" s="38">
+        <f>G51</f>
+        <v>444.92574257425741</v>
+      </c>
+      <c r="I51" s="38">
+        <f>H51</f>
+        <v>444.92574257425741</v>
+      </c>
+      <c r="J51" s="38">
+        <f>I51</f>
+        <v>444.92574257425741</v>
+      </c>
+      <c r="L51"/>
+    </row>
+    <row r="52" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="7">
+        <v>0.624</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" s="39">
+        <v>1000</v>
+      </c>
+      <c r="E52" s="39">
+        <v>1000</v>
+      </c>
+      <c r="F52" s="39">
+        <v>1000</v>
+      </c>
+      <c r="G52" s="39">
+        <v>1000</v>
+      </c>
+      <c r="H52" s="39">
+        <v>1000</v>
+      </c>
+      <c r="I52" s="39">
+        <v>1000</v>
+      </c>
+      <c r="J52" s="39">
+        <v>1000</v>
+      </c>
+      <c r="L52"/>
+    </row>
+    <row r="53" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="8">
+        <f>B54-SUM(B37:B52)</f>
+        <v>203.49250000000001</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8">
+        <v>0</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8">
+        <v>0</v>
+      </c>
+      <c r="H53" s="8">
+        <v>0</v>
+      </c>
+      <c r="I53" s="8">
+        <v>0</v>
+      </c>
+      <c r="J53" s="8">
+        <v>0</v>
+      </c>
+      <c r="L53"/>
+    </row>
+    <row r="54" spans="1:32" s="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="8">
+        <v>329.5</v>
+      </c>
+      <c r="L54"/>
+    </row>
+    <row r="55" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
+    </row>
+    <row r="56" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="7"/>
+    </row>
+    <row r="57" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A57" s="14"/>
+    </row>
+    <row r="58" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A58" s="5"/>
+    </row>
+    <row r="59" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59">
         <v>0.78500000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A39" s="5"/>
-    </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A40" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="C41">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A60" s="5"/>
+    </row>
+    <row r="61" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A61" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="C62">
         <v>2021</v>
       </c>
-      <c r="D41">
+      <c r="D62">
         <v>2022</v>
       </c>
-      <c r="E41">
+      <c r="E62">
         <v>2023</v>
       </c>
-      <c r="F41">
+      <c r="F62">
         <v>2024</v>
       </c>
-      <c r="G41">
+      <c r="G62">
         <v>2025</v>
       </c>
-      <c r="H41">
+      <c r="H62">
         <v>2026</v>
       </c>
-      <c r="I41">
+      <c r="I62">
         <v>2027</v>
       </c>
-      <c r="J41">
+      <c r="J62">
         <v>2028</v>
       </c>
-      <c r="K41">
+      <c r="K62">
         <v>2029</v>
       </c>
-      <c r="L41">
+      <c r="L62">
         <v>2030</v>
       </c>
-      <c r="M41">
+      <c r="M62">
         <v>2031</v>
       </c>
-      <c r="N41">
+      <c r="N62">
         <v>2032</v>
       </c>
-      <c r="O41">
+      <c r="O62">
         <v>2033</v>
       </c>
-      <c r="P41">
+      <c r="P62">
         <v>2034</v>
       </c>
-      <c r="Q41">
+      <c r="Q62">
         <v>2035</v>
       </c>
-      <c r="R41">
+      <c r="R62">
         <v>2036</v>
       </c>
-      <c r="S41">
+      <c r="S62">
         <v>2037</v>
       </c>
-      <c r="T41">
+      <c r="T62">
         <v>2038</v>
       </c>
-      <c r="U41">
+      <c r="U62">
         <v>2039</v>
       </c>
-      <c r="V41">
+      <c r="V62">
         <v>2040</v>
       </c>
-      <c r="W41">
+      <c r="W62">
         <v>2041</v>
       </c>
-      <c r="X41">
+      <c r="X62">
         <v>2042</v>
       </c>
-      <c r="Y41">
+      <c r="Y62">
         <v>2043</v>
       </c>
-      <c r="Z41">
+      <c r="Z62">
         <v>2044</v>
       </c>
-      <c r="AA41">
+      <c r="AA62">
         <v>2045</v>
       </c>
-      <c r="AB41">
+      <c r="AB62">
         <v>2046</v>
       </c>
-      <c r="AC41">
+      <c r="AC62">
         <v>2047</v>
       </c>
-      <c r="AD41">
+      <c r="AD62">
         <v>2048</v>
       </c>
-      <c r="AE41">
+      <c r="AE62">
         <v>2049</v>
       </c>
-      <c r="AF41">
+      <c r="AF62">
         <v>2050</v>
       </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="C42" s="5">
-        <f t="shared" ref="C42:H42" si="5">SUMPRODUCT(E20:E33,$B$20:$B$33)/SUM($B$20:$B$33)*$B$38</f>
-        <v>600.15334597875574</v>
-      </c>
-      <c r="D42" s="5">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A63" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" s="5">
+        <f t="shared" ref="C63:H63" si="4">SUMPRODUCT(E17:E33,$B$17:$B$33)/SUM($B$17:$B$33)*L79</f>
+        <v>284.24236864339406</v>
+      </c>
+      <c r="D63" s="5">
+        <f t="shared" si="4"/>
+        <v>231.21682138187734</v>
+      </c>
+      <c r="E63" s="5">
+        <f t="shared" si="4"/>
+        <v>334.13793520947195</v>
+      </c>
+      <c r="F63" s="5">
+        <f t="shared" si="4"/>
+        <v>264.43888586266991</v>
+      </c>
+      <c r="G63" s="5">
+        <f t="shared" si="4"/>
+        <v>199.92712908586196</v>
+      </c>
+      <c r="H63" s="5">
+        <f t="shared" si="4"/>
+        <v>194.10400882122519</v>
+      </c>
+      <c r="I63" s="5">
+        <f>H63*R79/Q79</f>
+        <v>188.4504940011895</v>
+      </c>
+      <c r="J63" s="5">
+        <f t="shared" ref="J63:Q63" si="5">I63*S79/R79</f>
+        <v>182.96164466134903</v>
+      </c>
+      <c r="K63" s="5">
         <f t="shared" si="5"/>
-        <v>576.45146813353574</v>
-      </c>
-      <c r="E42" s="5">
+        <v>177.63266471975632</v>
+      </c>
+      <c r="L63" s="5">
         <f t="shared" si="5"/>
-        <v>576.45146813353574</v>
-      </c>
-      <c r="F42" s="5">
+        <v>172.45889778617118</v>
+      </c>
+      <c r="M63" s="5">
         <f t="shared" si="5"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="G42" s="5">
+        <v>167.43582309337009</v>
+      </c>
+      <c r="N63" s="5">
         <f t="shared" si="5"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="H42" s="5">
+        <v>162.55905154696123</v>
+      </c>
+      <c r="O63" s="5">
         <f t="shared" si="5"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="I42" s="5">
-        <f>H42</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="J42" s="5">
-        <f t="shared" ref="J42:AF42" si="6">I42</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="K42" s="5">
+        <v>157.82432189025366</v>
+      </c>
+      <c r="P63" s="5">
+        <f t="shared" si="5"/>
+        <v>153.22749698082879</v>
+      </c>
+      <c r="Q63" s="5">
+        <f t="shared" si="5"/>
+        <v>148.76456017556194</v>
+      </c>
+      <c r="R63" s="5">
+        <v>0</v>
+      </c>
+      <c r="S63" s="5">
+        <v>0</v>
+      </c>
+      <c r="T63" s="5">
+        <v>0</v>
+      </c>
+      <c r="U63" s="5">
+        <v>0</v>
+      </c>
+      <c r="V63" s="5">
+        <v>0</v>
+      </c>
+      <c r="W63" s="5">
+        <v>0</v>
+      </c>
+      <c r="X63" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A64" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="5">
+        <f>SUMPRODUCT(E37:E53,$B$37:$B$53)/SUM($B$37:$B$53)*L79</f>
+        <v>215.72168420258612</v>
+      </c>
+      <c r="D64" s="5">
+        <f t="shared" ref="D64:H64" si="6">SUMPRODUCT(F37:F53,$B$37:$B$53)/SUM($B$37:$B$53)*M79</f>
+        <v>188.02811316670545</v>
+      </c>
+      <c r="E64" s="5">
         <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="L42" s="5">
+        <v>181.15698643889937</v>
+      </c>
+      <c r="F64" s="5">
         <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="M42" s="5">
+        <v>152.76346597230366</v>
+      </c>
+      <c r="G64" s="5">
         <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="N42" s="5">
+        <v>96.20855199074947</v>
+      </c>
+      <c r="H64" s="5">
         <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="O42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AF42" s="5">
-        <f t="shared" si="6"/>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A43" s="5"/>
-    </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="C45">
+        <v>93.406361156067433</v>
+      </c>
+      <c r="I64" s="5">
+        <f>H64*R79/Q79</f>
+        <v>90.685787530162571</v>
+      </c>
+      <c r="J64" s="5">
+        <f t="shared" ref="J64:Q64" si="7">I64*S79/R79</f>
+        <v>88.04445391277919</v>
+      </c>
+      <c r="K64" s="5">
+        <f t="shared" si="7"/>
+        <v>85.480052342504052</v>
+      </c>
+      <c r="L64" s="5">
+        <f t="shared" si="7"/>
+        <v>82.990342080101016</v>
+      </c>
+      <c r="M64" s="5">
+        <f t="shared" si="7"/>
+        <v>80.573147650583522</v>
+      </c>
+      <c r="N64" s="5">
+        <f t="shared" si="7"/>
+        <v>78.226356942314084</v>
+      </c>
+      <c r="O64" s="5">
+        <f t="shared" si="7"/>
+        <v>75.947919361469985</v>
+      </c>
+      <c r="P64" s="5">
+        <f t="shared" si="7"/>
+        <v>73.735844040262123</v>
+      </c>
+      <c r="Q64" s="5">
+        <f t="shared" si="7"/>
+        <v>71.588198097341873</v>
+      </c>
+      <c r="R64" s="5">
+        <v>0</v>
+      </c>
+      <c r="S64" s="5">
+        <v>0</v>
+      </c>
+      <c r="T64" s="5">
+        <v>0</v>
+      </c>
+      <c r="U64" s="5">
+        <v>0</v>
+      </c>
+      <c r="V64" s="5">
+        <v>0</v>
+      </c>
+      <c r="W64" s="5">
+        <v>0</v>
+      </c>
+      <c r="X64" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A65" s="5"/>
+    </row>
+    <row r="66" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A66" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="67" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="C67">
         <v>2021</v>
       </c>
-      <c r="D45">
+      <c r="D67">
         <v>2022</v>
       </c>
-      <c r="E45">
+      <c r="E67">
         <v>2023</v>
       </c>
-      <c r="F45">
+      <c r="F67">
         <v>2024</v>
       </c>
-      <c r="G45">
+      <c r="G67">
         <v>2025</v>
       </c>
-      <c r="H45">
+      <c r="H67">
         <v>2026</v>
       </c>
-      <c r="I45">
+      <c r="I67">
         <v>2027</v>
       </c>
-      <c r="J45">
+      <c r="J67">
         <v>2028</v>
       </c>
-      <c r="K45">
+      <c r="K67">
         <v>2029</v>
       </c>
-      <c r="L45">
+      <c r="L67">
         <v>2030</v>
       </c>
-      <c r="M45">
+      <c r="M67">
         <v>2031</v>
       </c>
-      <c r="N45">
+      <c r="N67">
         <v>2032</v>
       </c>
-      <c r="O45">
+      <c r="O67">
         <v>2033</v>
       </c>
-      <c r="P45">
+      <c r="P67">
         <v>2034</v>
       </c>
-      <c r="Q45">
+      <c r="Q67">
         <v>2035</v>
       </c>
-      <c r="R45">
+      <c r="R67">
         <v>2036</v>
       </c>
-      <c r="S45">
+      <c r="S67">
         <v>2037</v>
       </c>
-      <c r="T45">
+      <c r="T67">
         <v>2038</v>
       </c>
-      <c r="U45">
+      <c r="U67">
         <v>2039</v>
       </c>
-      <c r="V45">
+      <c r="V67">
         <v>2040</v>
       </c>
-      <c r="W45">
+      <c r="W67">
         <v>2041</v>
       </c>
-      <c r="X45">
+      <c r="X67">
         <v>2042</v>
       </c>
-      <c r="Y45">
+      <c r="Y67">
         <v>2043</v>
       </c>
-      <c r="Z45">
+      <c r="Z67">
         <v>2044</v>
       </c>
-      <c r="AA45">
+      <c r="AA67">
         <v>2045</v>
       </c>
-      <c r="AB45">
+      <c r="AB67">
         <v>2046</v>
       </c>
-      <c r="AC45">
+      <c r="AC67">
         <v>2047</v>
       </c>
-      <c r="AD45">
+      <c r="AD67">
         <v>2048</v>
       </c>
-      <c r="AE45">
+      <c r="AE67">
         <v>2049</v>
       </c>
-      <c r="AF45">
+      <c r="AF67">
         <v>2050</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A46" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5">
-        <f t="shared" ref="C46:AF46" si="7">B4+C42</f>
-        <v>3036.0333459787557</v>
-      </c>
-      <c r="D46" s="5">
-        <f t="shared" si="7"/>
-        <v>2273.5314681335358</v>
-      </c>
-      <c r="E46" s="5">
-        <f t="shared" si="7"/>
-        <v>2371.7262681335355</v>
-      </c>
-      <c r="F46" s="5">
-        <f t="shared" si="7"/>
-        <v>2329.8343100151742</v>
-      </c>
-      <c r="G46" s="5">
-        <f t="shared" si="7"/>
-        <v>1671.1026100151744</v>
-      </c>
-      <c r="H46" s="5">
-        <f t="shared" si="7"/>
-        <v>1625.6076100151745</v>
-      </c>
-      <c r="I46" s="5">
-        <f t="shared" si="7"/>
-        <v>1591.1151100151747</v>
-      </c>
-      <c r="J46" s="5">
-        <f t="shared" si="7"/>
-        <v>1593.1401100151747</v>
-      </c>
-      <c r="K46" s="5">
-        <f t="shared" si="7"/>
-        <v>1599.8726100151744</v>
-      </c>
-      <c r="L46" s="5">
-        <f t="shared" si="7"/>
-        <v>1658.1326100151746</v>
-      </c>
-      <c r="M46" s="5">
-        <f t="shared" si="7"/>
-        <v>1713.9176100151744</v>
-      </c>
-      <c r="N46" s="5">
-        <f t="shared" si="7"/>
-        <v>1724.7001100151747</v>
-      </c>
-      <c r="O46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AF46" s="5">
-        <f t="shared" si="7"/>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" s="5">
-        <f t="shared" ref="C47:AF47" si="8">B5+C42</f>
-        <v>7252.8733459787563</v>
-      </c>
-      <c r="D47" s="5">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5">
+        <f t="shared" ref="C68:AF68" si="8">B5+C63</f>
+        <v>1930.7404811231229</v>
+      </c>
+      <c r="D68" s="5">
         <f t="shared" si="8"/>
-        <v>4193.501468133536</v>
-      </c>
-      <c r="E47" s="5">
+        <v>1599.8025784220101</v>
+      </c>
+      <c r="E68" s="5">
         <f t="shared" si="8"/>
-        <v>2371.7262681335355</v>
-      </c>
-      <c r="F47" s="5">
+        <v>5130.1015918271351</v>
+      </c>
+      <c r="F68" s="5">
         <f t="shared" si="8"/>
-        <v>2329.8343100151742</v>
-      </c>
-      <c r="G47" s="5">
+        <v>3819.9265877142789</v>
+      </c>
+      <c r="G68" s="5">
         <f t="shared" si="8"/>
-        <v>1671.1026100151744</v>
-      </c>
-      <c r="H47" s="5">
+        <v>3565.6148024975096</v>
+      </c>
+      <c r="H68" s="5">
         <f t="shared" si="8"/>
-        <v>1625.6076100151745</v>
-      </c>
-      <c r="I47" s="5">
+        <v>3312.3286898445285</v>
+      </c>
+      <c r="I68" s="5">
         <f t="shared" si="8"/>
-        <v>1591.1151100151747</v>
-      </c>
-      <c r="J47" s="5">
+        <v>2579.6280722494112</v>
+      </c>
+      <c r="J68" s="5">
         <f t="shared" si="8"/>
-        <v>1593.1401100151747</v>
-      </c>
-      <c r="K47" s="5">
+        <v>2607.4715657030551</v>
+      </c>
+      <c r="K68" s="5">
         <f t="shared" si="8"/>
-        <v>1599.8726100151744</v>
-      </c>
-      <c r="L47" s="5">
+        <v>2637.5199855509622</v>
+      </c>
+      <c r="L68" s="5">
         <f t="shared" si="8"/>
-        <v>1658.1326100151746</v>
-      </c>
-      <c r="M47" s="5">
+        <v>2669.5709726607206</v>
+      </c>
+      <c r="M68" s="5">
         <f t="shared" si="8"/>
-        <v>1713.9176100151744</v>
-      </c>
-      <c r="N47" s="5">
+        <v>2692.8330628056278</v>
+      </c>
+      <c r="N68" s="5">
         <f t="shared" si="8"/>
-        <v>1724.7001100151747</v>
-      </c>
-      <c r="O47" s="5">
+        <v>2715.0603144269971</v>
+      </c>
+      <c r="O68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P47" s="5">
+        <v>157.82432189025366</v>
+      </c>
+      <c r="P68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q47" s="5">
+        <v>153.22749698082879</v>
+      </c>
+      <c r="Q68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R47" s="5">
+        <v>148.76456017556194</v>
+      </c>
+      <c r="R68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S47" s="5">
+        <v>0</v>
+      </c>
+      <c r="S68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T47" s="5">
+        <v>0</v>
+      </c>
+      <c r="T68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U47" s="5">
+        <v>0</v>
+      </c>
+      <c r="U68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V47" s="5">
+        <v>0</v>
+      </c>
+      <c r="V68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W47" s="5">
+        <v>0</v>
+      </c>
+      <c r="W68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X47" s="5">
+        <v>0</v>
+      </c>
+      <c r="X68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y47" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z47" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AF47" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="5">
         <f t="shared" si="8"/>
-        <v>568.32511001517457</v>
-      </c>
-    </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B59" s="17"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A69" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="5">
+        <f>B6+C64</f>
+        <v>6868.4402011018146</v>
+      </c>
+      <c r="D69" s="5">
+        <f t="shared" ref="D69:AF69" si="9">C6+D64</f>
+        <v>3805.0788061456087</v>
+      </c>
+      <c r="E69" s="5">
+        <f t="shared" si="9"/>
+        <v>3662.355308727233</v>
+      </c>
+      <c r="F69" s="5">
+        <f t="shared" si="9"/>
+        <v>2999.2858045496764</v>
+      </c>
+      <c r="G69" s="5">
+        <f t="shared" si="9"/>
+        <v>2492.4252043210045</v>
+      </c>
+      <c r="H69" s="5">
+        <f t="shared" si="9"/>
+        <v>2355.6859555808901</v>
+      </c>
+      <c r="I69" s="5">
+        <f t="shared" si="9"/>
+        <v>2224.0661798520518</v>
+      </c>
+      <c r="J69" s="5">
+        <f t="shared" si="9"/>
+        <v>2167.4924466149887</v>
+      </c>
+      <c r="K69" s="5">
+        <f t="shared" si="9"/>
+        <v>2112.6190346880921</v>
+      </c>
+      <c r="L69" s="5">
+        <f t="shared" si="9"/>
+        <v>2059.3856145068316</v>
+      </c>
+      <c r="M69" s="5">
+        <f t="shared" si="9"/>
+        <v>2006.7216198707158</v>
+      </c>
+      <c r="N69" s="5">
+        <f t="shared" si="9"/>
+        <v>1955.3640812230597</v>
+      </c>
+      <c r="O69" s="5">
+        <f t="shared" si="9"/>
+        <v>75.947919361469985</v>
+      </c>
+      <c r="P69" s="5">
+        <f t="shared" si="9"/>
+        <v>73.735844040262123</v>
+      </c>
+      <c r="Q69" s="5">
+        <f t="shared" si="9"/>
+        <v>71.588198097341873</v>
+      </c>
+      <c r="R69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="T69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AC69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AD69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AE69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF69" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="D73" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+    </row>
+    <row r="74" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="D74" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+    </row>
+    <row r="75" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="D75" s="22">
+        <v>2020</v>
+      </c>
+      <c r="E75" s="22">
+        <v>2021</v>
+      </c>
+      <c r="F75" s="22">
+        <v>2022</v>
+      </c>
+      <c r="G75" s="22">
+        <v>2023</v>
+      </c>
+      <c r="H75" s="22">
+        <v>2024</v>
+      </c>
+      <c r="I75" s="22">
+        <v>2025</v>
+      </c>
+      <c r="J75" s="22">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="76" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="D76" s="40">
+        <v>0.2467</v>
+      </c>
+      <c r="E76" s="40">
+        <v>0.30919999999999997</v>
+      </c>
+      <c r="F76" s="40">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="G76" s="40">
+        <v>0.21729999999999999</v>
+      </c>
+      <c r="H76" s="40">
+        <v>0.46560000000000001</v>
+      </c>
+      <c r="I76" s="41">
+        <f>H76</f>
+        <v>0.46560000000000001</v>
+      </c>
+      <c r="J76" s="42">
+        <f>I76</f>
+        <v>0.46560000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="B78" s="22"/>
+      <c r="C78" s="22">
+        <v>2012</v>
+      </c>
+      <c r="D78" s="22">
+        <v>2013</v>
+      </c>
+      <c r="E78" s="22">
+        <v>2014</v>
+      </c>
+      <c r="F78" s="22">
+        <v>2015</v>
+      </c>
+      <c r="G78" s="22">
+        <v>2016</v>
+      </c>
+      <c r="H78" s="22">
+        <v>2017</v>
+      </c>
+      <c r="I78" s="22">
+        <v>2018</v>
+      </c>
+      <c r="J78" s="22">
+        <v>2019</v>
+      </c>
+      <c r="K78" s="22">
+        <v>2020</v>
+      </c>
+      <c r="L78" s="22">
+        <v>2021</v>
+      </c>
+      <c r="M78" s="22">
+        <v>2022</v>
+      </c>
+      <c r="N78" s="22">
+        <v>2023</v>
+      </c>
+      <c r="O78" s="22">
+        <v>2024</v>
+      </c>
+      <c r="P78" s="22">
+        <v>2025</v>
+      </c>
+      <c r="Q78" s="22">
+        <v>2026</v>
+      </c>
+      <c r="R78" s="22">
+        <v>2027</v>
+      </c>
+      <c r="S78" s="22">
+        <v>2028</v>
+      </c>
+      <c r="T78" s="22">
+        <v>2029</v>
+      </c>
+      <c r="U78" s="22">
+        <v>2030</v>
+      </c>
+      <c r="V78" s="22">
+        <v>2031</v>
+      </c>
+      <c r="W78" s="22">
+        <v>2032</v>
+      </c>
+      <c r="X78" s="22">
+        <v>2033</v>
+      </c>
+      <c r="Y78" s="22">
+        <v>2034</v>
+      </c>
+      <c r="Z78" s="22">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="79" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="B79" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C79" s="43" cm="1">
+        <f t="array" ref="C79:Z79">TRANSPOSE(G84:G107)</f>
+        <v>1</v>
+      </c>
+      <c r="D79" s="43">
+        <v>0.98556385942470071</v>
+      </c>
+      <c r="E79" s="43">
+        <v>0.96983137334414704</v>
+      </c>
+      <c r="F79" s="43">
+        <v>0.9686815713640794</v>
+      </c>
+      <c r="G79" s="43">
+        <v>0.95661376543184151</v>
+      </c>
+      <c r="H79" s="43">
+        <v>0.93665959530026111</v>
+      </c>
+      <c r="I79" s="43">
+        <v>0.9143273584567535</v>
+      </c>
+      <c r="J79" s="43">
+        <v>0.89805481563188172</v>
+      </c>
+      <c r="K79" s="43">
+        <v>0.88711067149387013</v>
+      </c>
+      <c r="L79" s="43">
+        <v>0.84730412960844359</v>
+      </c>
+      <c r="M79" s="43">
+        <v>0.78452102304761584</v>
+      </c>
+      <c r="N79" s="43">
+        <v>0.75350342301658668</v>
+      </c>
+      <c r="O79" s="43">
+        <v>0.73191600598044548</v>
+      </c>
+      <c r="P79" s="44">
+        <v>0.71059806405868498</v>
+      </c>
+      <c r="Q79" s="44">
+        <v>0.68990103306668438</v>
+      </c>
+      <c r="R79" s="44">
+        <v>0.66980682822008197</v>
+      </c>
+      <c r="S79" s="44">
+        <v>0.65029789147580774</v>
+      </c>
+      <c r="T79" s="44">
+        <v>0.63135717619010456</v>
+      </c>
+      <c r="U79" s="44">
+        <v>0.61296813222340252</v>
+      </c>
+      <c r="V79" s="44">
+        <v>0.59511469147903162</v>
+      </c>
+      <c r="W79" s="44">
+        <v>0.57778125386313739</v>
+      </c>
+      <c r="X79" s="44">
+        <v>0.56095267365353152</v>
+      </c>
+      <c r="Y79" s="44">
+        <v>0.54461424626556454</v>
+      </c>
+      <c r="Z79" s="44">
+        <v>0.52875169540346068</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>103</v>
+      </c>
+      <c r="B82" s="16"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="E82" s="17"/>
+      <c r="F82" s="17"/>
+      <c r="G82" s="17">
+        <v>0.03</v>
+      </c>
+      <c r="H82" s="17"/>
+      <c r="I82" s="17"/>
+      <c r="J82" s="17"/>
+      <c r="K82" s="17"/>
+      <c r="L82" s="15"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>104</v>
+      </c>
+      <c r="B84">
+        <v>228.85</v>
+      </c>
+      <c r="C84">
+        <v>230.33799999999999</v>
+      </c>
+      <c r="D84">
+        <v>229.59399999999999</v>
+      </c>
+      <c r="E84">
+        <v>1.7</v>
+      </c>
+      <c r="F84">
+        <v>2.1</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85">
+        <v>232.36600000000001</v>
+      </c>
+      <c r="C85">
+        <v>233.548</v>
+      </c>
+      <c r="D85">
+        <v>232.95699999999999</v>
+      </c>
+      <c r="E85">
+        <v>1.5</v>
+      </c>
+      <c r="F85">
+        <v>1.5</v>
+      </c>
+      <c r="G85">
+        <v>0.98556385942470071</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86">
+        <v>236.38399999999999</v>
+      </c>
+      <c r="C86">
+        <v>237.08799999999999</v>
+      </c>
+      <c r="D86">
+        <v>236.73599999999999</v>
+      </c>
+      <c r="E86">
+        <v>0.8</v>
+      </c>
+      <c r="F86">
+        <v>1.6</v>
+      </c>
+      <c r="G86">
+        <v>0.96983137334414704</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>107</v>
+      </c>
+      <c r="B87">
+        <v>236.26499999999999</v>
+      </c>
+      <c r="C87">
+        <v>237.76900000000001</v>
+      </c>
+      <c r="D87">
+        <v>237.017</v>
+      </c>
+      <c r="E87">
+        <v>0.7</v>
+      </c>
+      <c r="F87">
+        <v>0.1</v>
+      </c>
+      <c r="G87">
+        <v>0.9686815713640794</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>108</v>
+      </c>
+      <c r="B88">
+        <v>238.77799999999999</v>
+      </c>
+      <c r="C88">
+        <v>241.23699999999999</v>
+      </c>
+      <c r="D88">
+        <v>240.00700000000001</v>
+      </c>
+      <c r="E88">
+        <v>2.1</v>
+      </c>
+      <c r="F88">
+        <v>1.3</v>
+      </c>
+      <c r="G88">
+        <v>0.95661376543184151</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>109</v>
+      </c>
+      <c r="B89">
+        <v>244.07599999999999</v>
+      </c>
+      <c r="C89">
+        <v>246.16300000000001</v>
+      </c>
+      <c r="D89">
+        <v>245.12</v>
+      </c>
+      <c r="E89">
+        <v>2.1</v>
+      </c>
+      <c r="F89">
+        <v>2.1</v>
+      </c>
+      <c r="G89">
+        <v>0.93665959530026111</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>110</v>
+      </c>
+      <c r="B90">
+        <v>250.089</v>
+      </c>
+      <c r="C90">
+        <v>252.125</v>
+      </c>
+      <c r="D90">
+        <v>251.107</v>
+      </c>
+      <c r="E90">
+        <v>1.9</v>
+      </c>
+      <c r="F90">
+        <v>2.4</v>
+      </c>
+      <c r="G90">
+        <v>0.9143273584567535</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>111</v>
+      </c>
+      <c r="B91">
+        <v>254.41200000000001</v>
+      </c>
+      <c r="C91">
+        <v>256.90300000000002</v>
+      </c>
+      <c r="D91">
+        <v>255.65700000000001</v>
+      </c>
+      <c r="E91">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F91">
+        <v>1.8</v>
+      </c>
+      <c r="G91">
+        <v>0.89805481563188172</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>112</v>
+      </c>
+      <c r="B92">
+        <v>257.55700000000002</v>
+      </c>
+      <c r="C92">
+        <v>260.065</v>
+      </c>
+      <c r="D92">
+        <v>258.81099999999998</v>
+      </c>
+      <c r="E92">
+        <v>1.4</v>
+      </c>
+      <c r="F92">
+        <v>1.2</v>
+      </c>
+      <c r="G92">
+        <v>0.88711067149387013</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93">
+        <v>266.23599999999999</v>
+      </c>
+      <c r="C93">
+        <v>275.70299999999997</v>
+      </c>
+      <c r="D93">
+        <v>270.97000000000003</v>
+      </c>
+      <c r="E93">
+        <v>7</v>
+      </c>
+      <c r="F93">
+        <v>4.7</v>
+      </c>
+      <c r="G93">
+        <v>0.84730412960844359</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>114</v>
+      </c>
+      <c r="B94">
+        <v>288.34699999999998</v>
+      </c>
+      <c r="C94">
+        <v>296.96300000000002</v>
+      </c>
+      <c r="D94">
+        <v>292.65499999999997</v>
+      </c>
+      <c r="E94">
+        <v>6.5</v>
+      </c>
+      <c r="F94">
+        <v>8</v>
+      </c>
+      <c r="G94">
+        <v>0.78452102304761584</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>115</v>
+      </c>
+      <c r="B95">
+        <v>302.40800000000002</v>
+      </c>
+      <c r="C95">
+        <v>306.99599999999998</v>
+      </c>
+      <c r="D95">
+        <v>304.702</v>
+      </c>
+      <c r="G95">
+        <v>0.75350342301658668</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>116</v>
+      </c>
+      <c r="B96">
+        <v>312.14499999999998</v>
+      </c>
+      <c r="C96">
+        <v>315.233</v>
+      </c>
+      <c r="D96">
+        <v>313.68900000000002</v>
+      </c>
+      <c r="G96">
+        <v>0.73191600598044548</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>2025</v>
+      </c>
+      <c r="D97">
+        <f>D96*(1+F97)</f>
+        <v>323.09967</v>
+      </c>
+      <c r="F97" s="16">
+        <f>G$82</f>
+        <v>0.03</v>
+      </c>
+      <c r="G97" s="22">
+        <f>D$84/D97</f>
+        <v>0.71059806405868498</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>2026</v>
+      </c>
+      <c r="D98">
+        <f>D97*(1+F98)</f>
+        <v>332.79266010000003</v>
+      </c>
+      <c r="F98" s="16">
+        <f t="shared" ref="F98:F107" si="10">G$82</f>
+        <v>0.03</v>
+      </c>
+      <c r="G98" s="22">
+        <f t="shared" ref="G98:G107" si="11">D$84/D98</f>
+        <v>0.68990103306668438</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>2027</v>
+      </c>
+      <c r="D99">
+        <f t="shared" ref="D99:D107" si="12">D98*(1+F99)</f>
+        <v>342.77643990300004</v>
+      </c>
+      <c r="F99" s="16">
+        <f t="shared" si="10"/>
+        <v>0.03</v>
+      </c>
+      <c r="G99" s="22">
+        <f t="shared" si="11"/>
+        <v>0.66980682822008197</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>2028</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="12"/>
+        <v>353.05973310009006</v>
+      </c>
+      <c r="F100" s="16">
+        <f t="shared" si="10"/>
+        <v>0.03</v>
+      </c>
+      <c r="G100" s="22">
+        <f t="shared" si="11"/>
+        <v>0.65029789147580774</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>2029</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="12"/>
+        <v>363.65152509309274</v>
+      </c>
+      <c r="F101" s="16">
+        <f t="shared" si="10"/>
+        <v>0.03</v>
+      </c>
+      <c r="G101" s="22">
+        <f t="shared" si="11"/>
+        <v>0.63135717619010456</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>2030</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="12"/>
+        <v>374.56107084588552</v>
+      </c>
+      <c r="F102" s="16">
+        <f t="shared" si="10"/>
+        <v>0.03</v>
+      </c>
+      <c r="G102" s="22">
+        <f t="shared" si="11"/>
+        <v>0.61296813222340252</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>2031</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="12"/>
+        <v>385.79790297126209</v>
+      </c>
+      <c r="F103" s="16">
+        <f t="shared" si="10"/>
+        <v>0.03</v>
+      </c>
+      <c r="G103" s="22">
+        <f t="shared" si="11"/>
+        <v>0.59511469147903162</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>2032</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="12"/>
+        <v>397.37184006039996</v>
+      </c>
+      <c r="F104" s="16">
+        <f t="shared" si="10"/>
+        <v>0.03</v>
+      </c>
+      <c r="G104" s="22">
+        <f t="shared" si="11"/>
+        <v>0.57778125386313739</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>2033</v>
+      </c>
+      <c r="D105">
+        <f t="shared" si="12"/>
+        <v>409.29299526221195</v>
+      </c>
+      <c r="F105" s="16">
+        <f t="shared" si="10"/>
+        <v>0.03</v>
+      </c>
+      <c r="G105" s="22">
+        <f t="shared" si="11"/>
+        <v>0.56095267365353152</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>2034</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="12"/>
+        <v>421.57178512007829</v>
+      </c>
+      <c r="F106" s="16">
+        <f t="shared" si="10"/>
+        <v>0.03</v>
+      </c>
+      <c r="G106" s="22">
+        <f t="shared" si="11"/>
+        <v>0.54461424626556454</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>2035</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="12"/>
+        <v>434.21893867368067</v>
+      </c>
+      <c r="F107" s="16">
+        <f t="shared" si="10"/>
+        <v>0.03</v>
+      </c>
+      <c r="G107" s="22">
+        <f t="shared" si="11"/>
+        <v>0.52875169540346068</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C16" r:id="rId1" xr:uid="{0B42DB82-B744-4AA0-B817-45B85EC34540}"/>
-    <hyperlink ref="C17" r:id="rId2" xr:uid="{C245D4AA-4F3C-42F0-8772-AD708218D115}"/>
-    <hyperlink ref="R21" r:id="rId3" xr:uid="{52E38CEB-73A7-4855-878F-13F2616EA324}"/>
+    <hyperlink ref="C13" r:id="rId1" xr:uid="{0B42DB82-B744-4AA0-B817-45B85EC34540}"/>
+    <hyperlink ref="C14" r:id="rId2" xr:uid="{C245D4AA-4F3C-42F0-8772-AD708218D115}"/>
+    <hyperlink ref="R18" r:id="rId3" xr:uid="{5F06F0E1-C2F5-4064-8449-00379A1A43C2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -8410,1111 +10016,1047 @@
   <dimension ref="A1:AL776"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.81640625" style="23" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" style="23" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" style="23" customWidth="1"/>
-    <col min="5" max="38" width="7.54296875" style="23" customWidth="1"/>
-    <col min="39" max="16384" width="12.54296875" style="23"/>
+    <col min="1" max="1" width="51.81640625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" style="22" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="22" customWidth="1"/>
+    <col min="5" max="38" width="7.54296875" style="22" customWidth="1"/>
+    <col min="39" max="16384" width="12.54296875" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="22"/>
-      <c r="AJ1" s="22"/>
-      <c r="AK1" s="22"/>
-      <c r="AL1" s="22"/>
+      <c r="A1" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+      <c r="Z1" s="21"/>
+      <c r="AA1" s="21"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
+      <c r="AE1" s="21"/>
+      <c r="AF1" s="21"/>
+      <c r="AG1" s="21"/>
+      <c r="AH1" s="21"/>
+      <c r="AI1" s="21"/>
+      <c r="AJ1" s="21"/>
+      <c r="AK1" s="21"/>
+      <c r="AL1" s="21"/>
     </row>
     <row r="2" spans="1:38" ht="104.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="25"/>
-      <c r="AJ2" s="25"/>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="25"/>
+      <c r="A2" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
+      <c r="AH2" s="24"/>
+      <c r="AI2" s="24"/>
+      <c r="AJ2" s="24"/>
+      <c r="AK2" s="24"/>
+      <c r="AL2" s="24"/>
     </row>
     <row r="3" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
-      <c r="AD3" s="25"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="25"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="25"/>
-      <c r="AL3" s="25"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="24"/>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="24"/>
+      <c r="AH3" s="24"/>
+      <c r="AI3" s="24"/>
+      <c r="AJ3" s="24"/>
+      <c r="AK3" s="24"/>
+      <c r="AL3" s="24"/>
     </row>
     <row r="4" spans="1:38" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="35">
+      <c r="A4" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="34">
         <v>40000</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="25"/>
-      <c r="V4" s="25"/>
-      <c r="W4" s="25"/>
-      <c r="X4" s="25"/>
-      <c r="Y4" s="25"/>
-      <c r="Z4" s="25"/>
-      <c r="AA4" s="25"/>
-      <c r="AB4" s="25"/>
-      <c r="AC4" s="25"/>
-      <c r="AD4" s="25"/>
-      <c r="AE4" s="25"/>
-      <c r="AF4" s="25"/>
-      <c r="AG4" s="25"/>
-      <c r="AH4" s="25"/>
-      <c r="AI4" s="25"/>
-      <c r="AJ4" s="25"/>
-      <c r="AK4" s="25"/>
-      <c r="AL4" s="25"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="24"/>
+      <c r="AI4" s="24"/>
+      <c r="AJ4" s="24"/>
+      <c r="AK4" s="24"/>
+      <c r="AL4" s="24"/>
     </row>
     <row r="5" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="35">
+      <c r="A5" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="34">
         <v>7500</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
-      <c r="Y5" s="25"/>
-      <c r="Z5" s="25"/>
-      <c r="AA5" s="25"/>
-      <c r="AB5" s="25"/>
-      <c r="AC5" s="25"/>
-      <c r="AD5" s="25"/>
-      <c r="AE5" s="25"/>
-      <c r="AF5" s="25"/>
-      <c r="AG5" s="25"/>
-      <c r="AH5" s="25"/>
-      <c r="AI5" s="25"/>
-      <c r="AJ5" s="25"/>
-      <c r="AK5" s="25"/>
-      <c r="AL5" s="25"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="24"/>
+      <c r="AA5" s="24"/>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="24"/>
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="24"/>
+      <c r="AI5" s="24"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
+      <c r="AL5" s="24"/>
     </row>
     <row r="6" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="25"/>
-      <c r="U6" s="25"/>
-      <c r="V6" s="25"/>
-      <c r="W6" s="25"/>
-      <c r="X6" s="25"/>
-      <c r="Y6" s="25"/>
-      <c r="Z6" s="25"/>
-      <c r="AA6" s="25"/>
-      <c r="AB6" s="25"/>
-      <c r="AC6" s="25"/>
-      <c r="AD6" s="25"/>
-      <c r="AE6" s="25"/>
-      <c r="AF6" s="25"/>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="25"/>
-      <c r="AI6" s="25"/>
-      <c r="AJ6" s="25"/>
-      <c r="AK6" s="25"/>
-      <c r="AL6" s="25"/>
-    </row>
-    <row r="7" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="27">
-        <f>B4*$B$16*$B$14</f>
-        <v>27004</v>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="24"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="24"/>
+      <c r="AI6" s="24"/>
+      <c r="AJ6" s="24"/>
+      <c r="AK6" s="24"/>
+      <c r="AL6" s="24"/>
+    </row>
+    <row r="7" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="22">
+        <v>2023</v>
+      </c>
+      <c r="C7" s="22">
+        <v>2024</v>
+      </c>
+      <c r="D7" s="22">
+        <v>2025</v>
+      </c>
+      <c r="E7" s="22">
+        <v>2026</v>
+      </c>
+      <c r="F7" s="22">
+        <v>2027</v>
+      </c>
+      <c r="G7" s="22">
+        <v>2028</v>
+      </c>
+      <c r="H7" s="22">
+        <v>2029</v>
+      </c>
+      <c r="I7" s="22">
+        <v>2030</v>
+      </c>
+      <c r="J7" s="22">
+        <v>2031</v>
+      </c>
+      <c r="K7" s="22">
+        <v>2032</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="27">
-        <f>B4*B14</f>
-        <v>31400</v>
+      <c r="A8" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="26">
+        <f t="shared" ref="B8:K8" si="0">$B4*$B$16*C$14</f>
+        <v>25920.517751770582</v>
+      </c>
+      <c r="C8" s="26">
+        <f t="shared" si="0"/>
+        <v>25177.910605727324</v>
+      </c>
+      <c r="D8" s="26">
+        <f t="shared" si="0"/>
+        <v>24444.573403618764</v>
+      </c>
+      <c r="E8" s="26">
+        <f t="shared" si="0"/>
+        <v>23732.595537493944</v>
+      </c>
+      <c r="F8" s="26">
+        <f t="shared" si="0"/>
+        <v>23041.354890770821</v>
+      </c>
+      <c r="G8" s="26">
+        <f t="shared" si="0"/>
+        <v>22370.247466767785</v>
+      </c>
+      <c r="H8" s="26">
+        <f t="shared" si="0"/>
+        <v>21718.686860939597</v>
+      </c>
+      <c r="I8" s="26">
+        <f t="shared" si="0"/>
+        <v>21086.103748485046</v>
+      </c>
+      <c r="J8" s="26">
+        <f t="shared" si="0"/>
+        <v>20471.945386878688</v>
+      </c>
+      <c r="K8" s="26">
+        <f t="shared" si="0"/>
+        <v>19875.675132891927</v>
       </c>
     </row>
     <row r="9" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="27"/>
+      <c r="A9" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="26">
+        <f>$B$4*C14</f>
+        <v>30140.136920663466</v>
+      </c>
+      <c r="C9" s="26">
+        <f t="shared" ref="C9:K9" si="1">$B$4*D14</f>
+        <v>29276.640239217821</v>
+      </c>
+      <c r="D9" s="26">
+        <f t="shared" si="1"/>
+        <v>28423.922562347398</v>
+      </c>
+      <c r="E9" s="26">
+        <f t="shared" si="1"/>
+        <v>27596.041322667374</v>
+      </c>
+      <c r="F9" s="26">
+        <f t="shared" si="1"/>
+        <v>26792.273128803277</v>
+      </c>
+      <c r="G9" s="26">
+        <f t="shared" si="1"/>
+        <v>26011.915659032311</v>
+      </c>
+      <c r="H9" s="26">
+        <f t="shared" si="1"/>
+        <v>25254.287047604183</v>
+      </c>
+      <c r="I9" s="26">
+        <f t="shared" si="1"/>
+        <v>24518.725288936101</v>
+      </c>
+      <c r="J9" s="26">
+        <f t="shared" si="1"/>
+        <v>23804.587659161265</v>
+      </c>
+      <c r="K9" s="26">
+        <f t="shared" si="1"/>
+        <v>23111.250154525496</v>
+      </c>
     </row>
     <row r="10" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="23">
+      <c r="A10" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="35">
+        <f>C36</f>
+        <v>9715.0710076103514</v>
+      </c>
+      <c r="C10" s="35">
+        <f t="shared" ref="C10:K10" si="2">D36</f>
+        <v>9379.5012804435319</v>
+      </c>
+      <c r="D10" s="35">
+        <f t="shared" si="2"/>
+        <v>9098.157067904207</v>
+      </c>
+      <c r="E10" s="35">
+        <f t="shared" si="2"/>
+        <v>8900.5394373583313</v>
+      </c>
+      <c r="F10" s="35">
+        <f t="shared" si="2"/>
+        <v>8762.1955571514172</v>
+      </c>
+      <c r="G10" s="35">
+        <f t="shared" si="2"/>
+        <v>8574.638599520662</v>
+      </c>
+      <c r="H10" s="35">
+        <f t="shared" si="2"/>
+        <v>8327.2183891071436</v>
+      </c>
+      <c r="I10" s="35">
+        <f t="shared" si="2"/>
+        <v>8038.2687173078502</v>
+      </c>
+      <c r="J10" s="35">
+        <f t="shared" si="2"/>
+        <v>7772.0490463949827</v>
+      </c>
+      <c r="K10" s="35">
+        <f t="shared" si="2"/>
+        <v>7566.1942040579743</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="21"/>
+      <c r="AC12" s="21"/>
+      <c r="AD12" s="21"/>
+      <c r="AE12" s="21"/>
+      <c r="AF12" s="21"/>
+      <c r="AG12" s="21"/>
+      <c r="AH12" s="21"/>
+      <c r="AI12" s="21"/>
+      <c r="AJ12" s="21"/>
+      <c r="AK12" s="21"/>
+      <c r="AL12" s="21"/>
+    </row>
+    <row r="13" spans="1:38" ht="13" x14ac:dyDescent="0.3">
+      <c r="B13" s="25">
+        <v>2022</v>
+      </c>
+      <c r="C13" s="22">
         <v>2023</v>
       </c>
-      <c r="C10" s="23">
+      <c r="D13" s="25">
         <v>2024</v>
       </c>
-      <c r="D10" s="23">
+      <c r="E13" s="22">
         <v>2025</v>
       </c>
-      <c r="E10" s="23">
+      <c r="F13" s="25">
         <v>2026</v>
       </c>
-      <c r="F10" s="23">
+      <c r="G13" s="22">
         <v>2027</v>
       </c>
-      <c r="G10" s="23">
+      <c r="H13" s="25">
         <v>2028</v>
       </c>
-      <c r="H10" s="23">
+      <c r="I13" s="22">
         <v>2029</v>
       </c>
-      <c r="I10" s="23">
+      <c r="J13" s="25">
         <v>2030</v>
       </c>
-      <c r="J10" s="23">
+      <c r="K13" s="22">
         <v>2031</v>
       </c>
-      <c r="K10" s="23">
+      <c r="L13" s="25">
         <v>2032</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="36">
-        <f>C36</f>
-        <v>10121.162702145082</v>
-      </c>
-      <c r="C11" s="36">
-        <f t="shared" ref="C11:K11" si="0">D36</f>
-        <v>10059.772494365814</v>
-      </c>
-      <c r="D11" s="36">
-        <f t="shared" si="0"/>
-        <v>10050.763799597085</v>
-      </c>
-      <c r="E11" s="36">
-        <f t="shared" si="0"/>
-        <v>10127.428607069427</v>
-      </c>
-      <c r="F11" s="36">
-        <f t="shared" si="0"/>
-        <v>10269.11524721545</v>
-      </c>
-      <c r="G11" s="36">
-        <f t="shared" si="0"/>
-        <v>10350.781370900584</v>
-      </c>
-      <c r="H11" s="36">
-        <f t="shared" si="0"/>
-        <v>10353.674088089921</v>
-      </c>
-      <c r="I11" s="36">
-        <f t="shared" si="0"/>
-        <v>10294.239800360298</v>
-      </c>
-      <c r="J11" s="36">
-        <f t="shared" si="0"/>
-        <v>10251.903689786537</v>
-      </c>
-      <c r="K11" s="36">
-        <f t="shared" si="0"/>
-        <v>10279.777009851599</v>
-      </c>
-    </row>
-    <row r="13" spans="1:38" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="22"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="22"/>
-      <c r="AF13" s="22"/>
-      <c r="AG13" s="22"/>
-      <c r="AH13" s="22"/>
-      <c r="AI13" s="22"/>
-      <c r="AJ13" s="22"/>
-      <c r="AK13" s="22"/>
-      <c r="AL13" s="22"/>
-    </row>
     <row r="14" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="26">
-        <v>0.78500000000000003</v>
+      <c r="A14" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="49" cm="1">
+        <f t="array" ref="B14:L14">TRANSPOSE('Passenger Vehicle Calculations'!G94:G104)</f>
+        <v>0.78452102304761584</v>
+      </c>
+      <c r="C14" s="50">
+        <v>0.75350342301658668</v>
+      </c>
+      <c r="D14" s="50">
+        <v>0.73191600598044548</v>
+      </c>
+      <c r="E14" s="50">
+        <v>0.71059806405868498</v>
+      </c>
+      <c r="F14" s="50">
+        <v>0.68990103306668438</v>
+      </c>
+      <c r="G14" s="50">
+        <v>0.66980682822008197</v>
+      </c>
+      <c r="H14" s="50">
+        <v>0.65029789147580774</v>
+      </c>
+      <c r="I14" s="50">
+        <v>0.63135717619010456</v>
+      </c>
+      <c r="J14" s="50">
+        <v>0.61296813222340252</v>
+      </c>
+      <c r="K14" s="50">
+        <v>0.59511469147903162</v>
+      </c>
+      <c r="L14" s="50">
+        <v>0.57778125386313739</v>
       </c>
     </row>
     <row r="15" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
+      <c r="A15" s="25"/>
     </row>
     <row r="16" spans="1:38" ht="13" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="26">
+      <c r="A16" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="25">
         <v>0.86</v>
       </c>
     </row>
     <row r="17" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
+      <c r="A17" s="25"/>
     </row>
     <row r="18" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A19" s="26" t="s">
-        <v>57</v>
+      <c r="A19" s="25" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A20" s="26" t="s">
-        <v>58</v>
+      <c r="A20" s="25" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:33" ht="39" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" ht="26" x14ac:dyDescent="0.3">
+      <c r="A23" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="26">
+        <f>B5*B14</f>
+        <v>5883.907672857119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" ht="26" x14ac:dyDescent="0.3">
+      <c r="A24" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B24" s="23">
+        <v>3</v>
+      </c>
+      <c r="C24" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="D24" s="26">
+        <f>D23</f>
+        <v>5883.907672857119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" ht="26" x14ac:dyDescent="0.3">
+      <c r="A25" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33" ht="26" x14ac:dyDescent="0.3">
-      <c r="A23" s="26" t="s">
+      <c r="B25" s="28">
+        <v>44657</v>
+      </c>
+      <c r="C25" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="27">
-        <f>B5*B14</f>
-        <v>5887.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33" ht="26" x14ac:dyDescent="0.3">
-      <c r="A24" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="24">
-        <v>3</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="27">
-        <f>D23</f>
-        <v>5887.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33" ht="26" x14ac:dyDescent="0.3">
-      <c r="A25" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="29">
-        <v>44657</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="27">
+      <c r="D25" s="26">
         <f>B4*B14</f>
-        <v>31400</v>
+        <v>31380.840921904633</v>
       </c>
     </row>
     <row r="26" spans="1:33" ht="13" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A27" s="26" t="s">
-        <v>69</v>
+      <c r="A27" s="25" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A28" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
-      <c r="AC28" s="30"/>
-      <c r="AD28" s="30"/>
-      <c r="AE28" s="30"/>
-      <c r="AF28" s="30"/>
-      <c r="AG28" s="30"/>
+      <c r="A28" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="29"/>
+      <c r="Z28" s="29"/>
+      <c r="AA28" s="29"/>
+      <c r="AB28" s="29"/>
+      <c r="AC28" s="29"/>
+      <c r="AD28" s="29"/>
+      <c r="AE28" s="29"/>
+      <c r="AF28" s="29"/>
+      <c r="AG28" s="29"/>
     </row>
     <row r="29" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A29" s="31"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
-      <c r="AE29" s="30"/>
-      <c r="AF29" s="30"/>
-      <c r="AG29" s="30"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
+      <c r="AA29" s="29"/>
+      <c r="AB29" s="29"/>
+      <c r="AC29" s="29"/>
+      <c r="AD29" s="29"/>
+      <c r="AE29" s="29"/>
+      <c r="AF29" s="29"/>
+      <c r="AG29" s="29"/>
     </row>
     <row r="30" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A30" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="30"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="30"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
-      <c r="Y30" s="30"/>
-      <c r="Z30" s="30"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="30"/>
-      <c r="AC30" s="30"/>
-      <c r="AD30" s="30"/>
-      <c r="AE30" s="30"/>
-      <c r="AF30" s="30"/>
-      <c r="AG30" s="30"/>
+      <c r="A30" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="29"/>
+      <c r="Z30" s="29"/>
+      <c r="AA30" s="29"/>
+      <c r="AB30" s="29"/>
+      <c r="AC30" s="29"/>
+      <c r="AD30" s="29"/>
+      <c r="AE30" s="29"/>
+      <c r="AF30" s="29"/>
+      <c r="AG30" s="29"/>
     </row>
     <row r="31" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="32">
+      <c r="A31" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="31">
         <v>2022</v>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="31">
         <v>2023</v>
       </c>
-      <c r="D31" s="32">
+      <c r="D31" s="31">
         <v>2024</v>
       </c>
-      <c r="E31" s="32">
+      <c r="E31" s="31">
         <v>2025</v>
       </c>
-      <c r="F31" s="32">
+      <c r="F31" s="31">
         <v>2026</v>
       </c>
-      <c r="G31" s="32">
+      <c r="G31" s="31">
         <v>2027</v>
       </c>
-      <c r="H31" s="32">
+      <c r="H31" s="31">
         <v>2028</v>
       </c>
-      <c r="I31" s="32">
+      <c r="I31" s="31">
         <v>2029</v>
       </c>
-      <c r="J31" s="32">
+      <c r="J31" s="31">
         <v>2030</v>
       </c>
-      <c r="K31" s="32">
+      <c r="K31" s="31">
         <v>2031</v>
       </c>
-      <c r="L31" s="32">
+      <c r="L31" s="31">
         <v>2032</v>
       </c>
-      <c r="M31" s="32">
-        <v>2033</v>
-      </c>
-      <c r="N31" s="32">
-        <v>2034</v>
-      </c>
-      <c r="O31" s="32">
-        <v>2035</v>
-      </c>
-      <c r="P31" s="32">
-        <v>2036</v>
-      </c>
-      <c r="Q31" s="32">
-        <v>2037</v>
-      </c>
-      <c r="R31" s="32">
-        <v>2038</v>
-      </c>
-      <c r="S31" s="32">
-        <v>2039</v>
-      </c>
-      <c r="T31" s="32">
-        <v>2040</v>
-      </c>
-      <c r="U31" s="32">
-        <v>2041</v>
-      </c>
-      <c r="V31" s="32">
-        <v>2042</v>
-      </c>
-      <c r="W31" s="32">
-        <v>2043</v>
-      </c>
-      <c r="X31" s="32">
-        <v>2044</v>
-      </c>
-      <c r="Y31" s="32">
-        <v>2045</v>
-      </c>
-      <c r="Z31" s="32">
-        <v>2046</v>
-      </c>
-      <c r="AA31" s="32">
-        <v>2047</v>
-      </c>
-      <c r="AB31" s="32">
-        <v>2048</v>
-      </c>
-      <c r="AC31" s="32">
-        <v>2049</v>
-      </c>
-      <c r="AD31" s="32">
-        <v>2050</v>
-      </c>
-      <c r="AE31" s="30"/>
-      <c r="AF31" s="30"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="31"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="31"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="31"/>
+      <c r="AB31" s="31"/>
+      <c r="AC31" s="31"/>
+      <c r="AD31" s="31"/>
+      <c r="AE31" s="29"/>
+      <c r="AF31" s="29"/>
     </row>
     <row r="32" spans="1:33" ht="13" x14ac:dyDescent="0.3">
-      <c r="A32" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="33">
+      <c r="A32" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="32">
         <v>652.15881300000001</v>
       </c>
-      <c r="C32" s="33">
+      <c r="C32" s="32">
         <v>675.13665800000001</v>
       </c>
-      <c r="D32" s="33">
+      <c r="D32" s="32">
         <v>689.60467500000004</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="32">
         <v>691.51690699999995</v>
       </c>
-      <c r="F32" s="33">
+      <c r="F32" s="32">
         <v>688.42425500000002</v>
       </c>
-      <c r="G32" s="33">
+      <c r="G32" s="32">
         <v>684.18414299999995</v>
       </c>
-      <c r="H32" s="33">
+      <c r="H32" s="32">
         <v>682.62188700000002</v>
       </c>
-      <c r="I32" s="33">
+      <c r="I32" s="32">
         <v>679.86218299999996</v>
       </c>
-      <c r="J32" s="33">
+      <c r="J32" s="32">
         <v>678.07775900000001</v>
       </c>
-      <c r="K32" s="33">
+      <c r="K32" s="32">
         <v>677.36639400000001</v>
       </c>
-      <c r="L32" s="33">
+      <c r="L32" s="32">
         <v>675.92620799999997</v>
       </c>
-      <c r="M32" s="33">
-        <v>676.86370799999997</v>
-      </c>
-      <c r="N32" s="33">
-        <v>681.45581100000004</v>
-      </c>
-      <c r="O32" s="33">
-        <v>687.30078100000003</v>
-      </c>
-      <c r="P32" s="33">
-        <v>692.37145999999996</v>
-      </c>
-      <c r="Q32" s="33">
-        <v>698.31860400000005</v>
-      </c>
-      <c r="R32" s="33">
-        <v>703.59320100000002</v>
-      </c>
-      <c r="S32" s="33">
-        <v>709.57092299999999</v>
-      </c>
-      <c r="T32" s="33">
-        <v>711.90655500000003</v>
-      </c>
-      <c r="U32" s="33">
-        <v>714.37567100000001</v>
-      </c>
-      <c r="V32" s="33">
-        <v>716.10638400000005</v>
-      </c>
-      <c r="W32" s="33">
-        <v>717.97564699999998</v>
-      </c>
-      <c r="X32" s="33">
-        <v>723.98962400000005</v>
-      </c>
-      <c r="Y32" s="33">
-        <v>729.19946300000004</v>
-      </c>
-      <c r="Z32" s="33">
-        <v>732.66320800000005</v>
-      </c>
-      <c r="AA32" s="33">
-        <v>734.38165300000003</v>
-      </c>
-      <c r="AB32" s="33">
-        <v>739.21014400000001</v>
-      </c>
-      <c r="AC32" s="33">
-        <v>745.07336399999997</v>
-      </c>
-      <c r="AD32" s="33">
-        <v>1035.5</v>
-      </c>
-      <c r="AE32" s="34"/>
-      <c r="AF32" s="30"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+      <c r="Z32" s="32"/>
+      <c r="AA32" s="32"/>
+      <c r="AB32" s="32"/>
+      <c r="AC32" s="32"/>
+      <c r="AD32" s="32"/>
+      <c r="AE32" s="33"/>
+      <c r="AF32" s="29"/>
     </row>
     <row r="33" spans="1:32" ht="13" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" s="33">
+      <c r="A33" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="32">
         <v>252.12297100000001</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="32">
         <v>262.199432</v>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="32">
         <v>276.18127399999997</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="32">
         <v>286.01892099999998</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="32">
         <v>290.46655299999998</v>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="32">
         <v>292.43240400000002</v>
       </c>
-      <c r="H33" s="33">
+      <c r="H33" s="32">
         <v>293.63424700000002</v>
       </c>
-      <c r="I33" s="33">
+      <c r="I33" s="32">
         <v>296.173248</v>
       </c>
-      <c r="J33" s="33">
+      <c r="J33" s="32">
         <v>298.12170400000002</v>
       </c>
-      <c r="K33" s="33">
+      <c r="K33" s="32">
         <v>300.39685100000003</v>
       </c>
-      <c r="L33" s="33">
+      <c r="L33" s="32">
         <v>303.257294</v>
       </c>
-      <c r="M33" s="33">
-        <v>305.71603399999998</v>
-      </c>
-      <c r="N33" s="33">
-        <v>309.26257299999997</v>
-      </c>
-      <c r="O33" s="33">
-        <v>314.79812600000002</v>
-      </c>
-      <c r="P33" s="33">
-        <v>321.14746100000002</v>
-      </c>
-      <c r="Q33" s="33">
-        <v>327.09249899999998</v>
-      </c>
-      <c r="R33" s="33">
-        <v>333.56478900000002</v>
-      </c>
-      <c r="S33" s="33">
-        <v>339.75351000000001</v>
-      </c>
-      <c r="T33" s="33">
-        <v>346.38189699999998</v>
-      </c>
-      <c r="U33" s="33">
-        <v>351.209137</v>
-      </c>
-      <c r="V33" s="33">
-        <v>355.95761099999999</v>
-      </c>
-      <c r="W33" s="33">
-        <v>360.42837500000002</v>
-      </c>
-      <c r="X33" s="33">
-        <v>364.902466</v>
-      </c>
-      <c r="Y33" s="33">
-        <v>371.72610500000002</v>
-      </c>
-      <c r="Z33" s="33">
-        <v>378.28823899999998</v>
-      </c>
-      <c r="AA33" s="33">
-        <v>383.89129600000001</v>
-      </c>
-      <c r="AB33" s="33">
-        <v>388.47567700000002</v>
-      </c>
-      <c r="AC33" s="33">
-        <v>394.81222500000001</v>
-      </c>
-      <c r="AD33" s="33">
-        <v>401.96115099999997</v>
-      </c>
-      <c r="AE33" s="34"/>
-      <c r="AF33" s="30"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="32"/>
+      <c r="Z33" s="32"/>
+      <c r="AA33" s="32"/>
+      <c r="AB33" s="32"/>
+      <c r="AC33" s="32"/>
+      <c r="AD33" s="32"/>
+      <c r="AE33" s="33"/>
+      <c r="AF33" s="29"/>
     </row>
     <row r="34" spans="1:32" ht="13" x14ac:dyDescent="0.3">
-      <c r="A34" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="33">
+      <c r="A34" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="32">
         <v>180.61982699999999</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="32">
         <v>186.49350000000001</v>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="32">
         <v>188.82283000000001</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="32">
         <v>190.626938</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="32">
         <v>195.106979</v>
       </c>
-      <c r="G34" s="33">
+      <c r="G34" s="32">
         <v>202.50727800000001</v>
       </c>
-      <c r="H34" s="33">
+      <c r="H34" s="32">
         <v>207.005585</v>
       </c>
-      <c r="I34" s="33">
+      <c r="I34" s="32">
         <v>207.12138400000001</v>
       </c>
-      <c r="J34" s="33">
+      <c r="J34" s="32">
         <v>203.823837</v>
       </c>
-      <c r="K34" s="33">
+      <c r="K34" s="32">
         <v>201.78428600000001</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="32">
         <v>203.63635300000001</v>
       </c>
-      <c r="M34" s="33">
-        <v>206.92961099999999</v>
-      </c>
-      <c r="N34" s="33">
-        <v>209.69859299999999</v>
-      </c>
-      <c r="O34" s="33">
-        <v>212.967072</v>
-      </c>
-      <c r="P34" s="33">
-        <v>216.125214</v>
-      </c>
-      <c r="Q34" s="33">
-        <v>219.188492</v>
-      </c>
-      <c r="R34" s="33">
-        <v>221.84333799999999</v>
-      </c>
-      <c r="S34" s="33">
-        <v>224.323059</v>
-      </c>
-      <c r="T34" s="33">
-        <v>227.32418799999999</v>
-      </c>
-      <c r="U34" s="33">
-        <v>230.371872</v>
-      </c>
-      <c r="V34" s="33">
-        <v>232.498154</v>
-      </c>
-      <c r="W34" s="33">
-        <v>235.21517900000001</v>
-      </c>
-      <c r="X34" s="33">
-        <v>236.05999800000001</v>
-      </c>
-      <c r="Y34" s="33">
-        <v>234.92872600000001</v>
-      </c>
-      <c r="Z34" s="33">
-        <v>234.37702899999999</v>
-      </c>
-      <c r="AA34" s="33">
-        <v>235.44674699999999</v>
-      </c>
-      <c r="AB34" s="33">
-        <v>237.52796900000001</v>
-      </c>
-      <c r="AC34" s="33">
-        <v>239.052933</v>
-      </c>
-      <c r="AD34" s="33">
-        <v>241.633881</v>
-      </c>
-      <c r="AE34" s="34"/>
-      <c r="AF34" s="30"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32"/>
+      <c r="P34" s="32"/>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="32"/>
+      <c r="U34" s="32"/>
+      <c r="V34" s="32"/>
+      <c r="W34" s="32"/>
+      <c r="X34" s="32"/>
+      <c r="Y34" s="32"/>
+      <c r="Z34" s="32"/>
+      <c r="AA34" s="32"/>
+      <c r="AB34" s="32"/>
+      <c r="AC34" s="32"/>
+      <c r="AD34" s="32"/>
+      <c r="AE34" s="33"/>
+      <c r="AF34" s="29"/>
     </row>
     <row r="36" spans="1:32" ht="13" x14ac:dyDescent="0.3">
-      <c r="A36" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="27">
-        <f t="shared" ref="B36:AD36" si="1">SUMPRODUCT(B32:B34,$D$23:$D$25)/SUM(B32:B34)</f>
-        <v>10134.948146095066</v>
-      </c>
-      <c r="C36" s="27">
-        <f t="shared" si="1"/>
-        <v>10121.162702145082</v>
-      </c>
-      <c r="D36" s="27">
-        <f t="shared" si="1"/>
-        <v>10059.772494365814</v>
-      </c>
-      <c r="E36" s="27">
-        <f t="shared" si="1"/>
-        <v>10050.763799597085</v>
-      </c>
-      <c r="F36" s="27">
-        <f t="shared" si="1"/>
-        <v>10127.428607069427</v>
-      </c>
-      <c r="G36" s="27">
-        <f t="shared" si="1"/>
-        <v>10269.11524721545</v>
-      </c>
-      <c r="H36" s="27">
-        <f t="shared" si="1"/>
-        <v>10350.781370900584</v>
-      </c>
-      <c r="I36" s="27">
-        <f t="shared" si="1"/>
-        <v>10353.674088089921</v>
-      </c>
-      <c r="J36" s="27">
-        <f t="shared" si="1"/>
-        <v>10294.239800360298</v>
-      </c>
-      <c r="K36" s="27">
-        <f t="shared" si="1"/>
-        <v>10251.903689786537</v>
-      </c>
-      <c r="L36" s="27">
-        <f t="shared" si="1"/>
-        <v>10279.777009851599</v>
-      </c>
-      <c r="M36" s="27">
-        <f t="shared" si="1"/>
-        <v>10325.709491436844</v>
-      </c>
-      <c r="N36" s="27">
-        <f t="shared" si="1"/>
-        <v>10344.230833049938</v>
-      </c>
-      <c r="O36" s="27">
-        <f t="shared" si="1"/>
-        <v>10359.12748221428</v>
-      </c>
-      <c r="P36" s="27">
-        <f t="shared" si="1"/>
-        <v>10371.638430973771</v>
-      </c>
-      <c r="Q36" s="27">
-        <f t="shared" si="1"/>
-        <v>10380.548547191598</v>
-      </c>
-      <c r="R36" s="27">
-        <f t="shared" si="1"/>
-        <v>10382.950508948947</v>
-      </c>
-      <c r="S36" s="27">
-        <f t="shared" si="1"/>
-        <v>10380.927010758403</v>
-      </c>
-      <c r="T36" s="27">
-        <f t="shared" si="1"/>
-        <v>10398.663134138134</v>
-      </c>
-      <c r="U36" s="27">
-        <f t="shared" si="1"/>
-        <v>10422.653431517481</v>
-      </c>
-      <c r="V36" s="27">
-        <f t="shared" si="1"/>
-        <v>10434.319910781423</v>
-      </c>
-      <c r="W36" s="27">
-        <f t="shared" si="1"/>
-        <v>10455.739600691937</v>
-      </c>
-      <c r="X36" s="27">
-        <f t="shared" si="1"/>
-        <v>10432.932814907192</v>
-      </c>
-      <c r="Y36" s="27">
-        <f t="shared" si="1"/>
-        <v>10374.231186923143</v>
-      </c>
-      <c r="Z36" s="27">
-        <f t="shared" si="1"/>
-        <v>10332.172107247137</v>
-      </c>
-      <c r="AA36" s="27">
-        <f t="shared" si="1"/>
-        <v>10324.781329795693</v>
-      </c>
-      <c r="AB36" s="27">
-        <f t="shared" si="1"/>
-        <v>10326.315629830769</v>
-      </c>
-      <c r="AC36" s="27">
-        <f t="shared" si="1"/>
-        <v>10310.34979051626</v>
-      </c>
-      <c r="AD36" s="27">
-        <f t="shared" si="1"/>
-        <v>9558.932689351499</v>
-      </c>
+      <c r="A36" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="26">
+        <f t="shared" ref="B36" si="3">SUMPRODUCT(B32:B34,$D$23:$D$25)/SUM(B32:B34)</f>
+        <v>10128.764188673933</v>
+      </c>
+      <c r="C36" s="26">
+        <f>SUMPRODUCT(C32:C34,$D$23:$D$25)/SUM(C32:C34)*C14/$B$14</f>
+        <v>9715.0710076103514</v>
+      </c>
+      <c r="D36" s="26">
+        <f t="shared" ref="D36:L36" si="4">SUMPRODUCT(D32:D34,$D$23:$D$25)/SUM(D32:D34)*D14/$B$14</f>
+        <v>9379.5012804435319</v>
+      </c>
+      <c r="E36" s="26">
+        <f t="shared" si="4"/>
+        <v>9098.157067904207</v>
+      </c>
+      <c r="F36" s="26">
+        <f t="shared" si="4"/>
+        <v>8900.5394373583313</v>
+      </c>
+      <c r="G36" s="26">
+        <f t="shared" si="4"/>
+        <v>8762.1955571514172</v>
+      </c>
+      <c r="H36" s="26">
+        <f t="shared" si="4"/>
+        <v>8574.638599520662</v>
+      </c>
+      <c r="I36" s="26">
+        <f t="shared" si="4"/>
+        <v>8327.2183891071436</v>
+      </c>
+      <c r="J36" s="26">
+        <f t="shared" si="4"/>
+        <v>8038.2687173078502</v>
+      </c>
+      <c r="K36" s="26">
+        <f t="shared" si="4"/>
+        <v>7772.0490463949827</v>
+      </c>
+      <c r="L36" s="26">
+        <f t="shared" si="4"/>
+        <v>7566.1942040579743</v>
+      </c>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="26"/>
+      <c r="S36" s="26"/>
+      <c r="T36" s="26"/>
+      <c r="U36" s="26"/>
+      <c r="V36" s="26"/>
+      <c r="W36" s="26"/>
+      <c r="X36" s="26"/>
+      <c r="Y36" s="26"/>
+      <c r="Z36" s="26"/>
+      <c r="AA36" s="26"/>
+      <c r="AB36" s="26"/>
+      <c r="AC36" s="26"/>
+      <c r="AD36" s="26"/>
     </row>
     <row r="37" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
     <row r="38" spans="1:32" ht="13" x14ac:dyDescent="0.3"/>
@@ -10385,219 +11927,219 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19">
-        <f>'Passenger Vehicle Calculations'!C46</f>
-        <v>3036.0333459787557</v>
-      </c>
-      <c r="C2" s="19">
-        <f>'Passenger Vehicle Calculations'!D46</f>
-        <v>2273.5314681335358</v>
-      </c>
-      <c r="D2" s="19">
-        <f>'Passenger Vehicle Calculations'!E46</f>
-        <v>2371.7262681335355</v>
-      </c>
-      <c r="E2" s="19">
-        <f>'Passenger Vehicle Calculations'!F46</f>
-        <v>2329.8343100151742</v>
-      </c>
-      <c r="F2" s="19">
-        <f>'Passenger Vehicle Calculations'!G46</f>
-        <v>1671.1026100151744</v>
-      </c>
-      <c r="G2" s="19">
-        <f>'Passenger Vehicle Calculations'!H46</f>
-        <v>1625.6076100151745</v>
-      </c>
-      <c r="H2" s="19">
-        <f>'Passenger Vehicle Calculations'!I46</f>
-        <v>1591.1151100151747</v>
-      </c>
-      <c r="I2" s="19">
-        <f>'Passenger Vehicle Calculations'!J46</f>
-        <v>1593.1401100151747</v>
-      </c>
-      <c r="J2" s="19">
-        <f>'Passenger Vehicle Calculations'!K46</f>
-        <v>1599.8726100151744</v>
-      </c>
-      <c r="K2" s="19">
-        <f>'Passenger Vehicle Calculations'!L46</f>
-        <v>1658.1326100151746</v>
-      </c>
-      <c r="L2" s="19">
-        <f>'Passenger Vehicle Calculations'!M46</f>
-        <v>1713.9176100151744</v>
-      </c>
-      <c r="M2" s="19">
-        <f>'Passenger Vehicle Calculations'!N46</f>
-        <v>1724.7001100151747</v>
-      </c>
-      <c r="N2" s="19">
-        <f>'Passenger Vehicle Calculations'!O46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="O2" s="19">
-        <f>'Passenger Vehicle Calculations'!P46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P2" s="19">
-        <f>'Passenger Vehicle Calculations'!Q46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q2" s="19">
-        <f>'Passenger Vehicle Calculations'!R46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R2" s="19">
-        <f>'Passenger Vehicle Calculations'!S46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S2" s="19">
-        <f>'Passenger Vehicle Calculations'!T46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T2" s="19">
-        <f>'Passenger Vehicle Calculations'!U46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U2" s="19">
-        <f>'Passenger Vehicle Calculations'!V46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V2" s="19">
-        <f>'Passenger Vehicle Calculations'!W46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W2" s="19">
-        <f>'Passenger Vehicle Calculations'!X46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X2" s="19">
-        <f>'Passenger Vehicle Calculations'!Y46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y2" s="19">
-        <f>'Passenger Vehicle Calculations'!Z46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z2" s="19">
-        <f>'Passenger Vehicle Calculations'!AA46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA2" s="19">
-        <f>'Passenger Vehicle Calculations'!AB46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB2" s="19">
-        <f>'Passenger Vehicle Calculations'!AC46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC2" s="19">
-        <f>'Passenger Vehicle Calculations'!AD46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD2" s="19">
-        <f>'Passenger Vehicle Calculations'!AE46</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE2" s="19">
-        <f>'Passenger Vehicle Calculations'!AF46</f>
-        <v>568.32511001517457</v>
+      <c r="B2" s="18">
+        <f>'Passenger Vehicle Calculations'!C68</f>
+        <v>1930.7404811231229</v>
+      </c>
+      <c r="C2" s="18">
+        <f>'Passenger Vehicle Calculations'!D68</f>
+        <v>1599.8025784220101</v>
+      </c>
+      <c r="D2" s="18">
+        <f>'Passenger Vehicle Calculations'!E68</f>
+        <v>5130.1015918271351</v>
+      </c>
+      <c r="E2" s="18">
+        <f>'Passenger Vehicle Calculations'!F68</f>
+        <v>3819.9265877142789</v>
+      </c>
+      <c r="F2" s="18">
+        <f>'Passenger Vehicle Calculations'!G68</f>
+        <v>3565.6148024975096</v>
+      </c>
+      <c r="G2" s="18">
+        <f>'Passenger Vehicle Calculations'!H68</f>
+        <v>3312.3286898445285</v>
+      </c>
+      <c r="H2" s="18">
+        <f>'Passenger Vehicle Calculations'!I68</f>
+        <v>2579.6280722494112</v>
+      </c>
+      <c r="I2" s="18">
+        <f>'Passenger Vehicle Calculations'!J68</f>
+        <v>2607.4715657030551</v>
+      </c>
+      <c r="J2" s="18">
+        <f>'Passenger Vehicle Calculations'!K68</f>
+        <v>2637.5199855509622</v>
+      </c>
+      <c r="K2" s="18">
+        <f>'Passenger Vehicle Calculations'!L68</f>
+        <v>2669.5709726607206</v>
+      </c>
+      <c r="L2" s="18">
+        <f>'Passenger Vehicle Calculations'!M68</f>
+        <v>2692.8330628056278</v>
+      </c>
+      <c r="M2" s="18">
+        <f>'Passenger Vehicle Calculations'!N68</f>
+        <v>2715.0603144269971</v>
+      </c>
+      <c r="N2" s="18">
+        <f>'Passenger Vehicle Calculations'!O68</f>
+        <v>157.82432189025366</v>
+      </c>
+      <c r="O2" s="18">
+        <f>'Passenger Vehicle Calculations'!P68</f>
+        <v>153.22749698082879</v>
+      </c>
+      <c r="P2" s="18">
+        <f>'Passenger Vehicle Calculations'!Q68</f>
+        <v>148.76456017556194</v>
+      </c>
+      <c r="Q2" s="18">
+        <f>'Passenger Vehicle Calculations'!R68</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="18">
+        <f>'Passenger Vehicle Calculations'!S68</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="18">
+        <f>'Passenger Vehicle Calculations'!T68</f>
+        <v>0</v>
+      </c>
+      <c r="T2" s="18">
+        <f>'Passenger Vehicle Calculations'!U68</f>
+        <v>0</v>
+      </c>
+      <c r="U2" s="18">
+        <f>'Passenger Vehicle Calculations'!V68</f>
+        <v>0</v>
+      </c>
+      <c r="V2" s="18">
+        <f>'Passenger Vehicle Calculations'!W68</f>
+        <v>0</v>
+      </c>
+      <c r="W2" s="18">
+        <f>'Passenger Vehicle Calculations'!X68</f>
+        <v>0</v>
+      </c>
+      <c r="X2" s="18">
+        <f>'Passenger Vehicle Calculations'!Y68</f>
+        <v>0</v>
+      </c>
+      <c r="Y2" s="18">
+        <f>'Passenger Vehicle Calculations'!Z68</f>
+        <v>0</v>
+      </c>
+      <c r="Z2" s="18">
+        <f>'Passenger Vehicle Calculations'!AA68</f>
+        <v>0</v>
+      </c>
+      <c r="AA2" s="18">
+        <f>'Passenger Vehicle Calculations'!AB68</f>
+        <v>0</v>
+      </c>
+      <c r="AB2" s="18">
+        <f>'Passenger Vehicle Calculations'!AC68</f>
+        <v>0</v>
+      </c>
+      <c r="AC2" s="18">
+        <f>'Passenger Vehicle Calculations'!AD68</f>
+        <v>0</v>
+      </c>
+      <c r="AD2" s="18">
+        <f>'Passenger Vehicle Calculations'!AE68</f>
+        <v>0</v>
+      </c>
+      <c r="AE2" s="18">
+        <f>'Passenger Vehicle Calculations'!AF68</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="19">
-        <v>0</v>
-      </c>
-      <c r="C3" s="19">
-        <v>0</v>
-      </c>
-      <c r="D3" s="19">
-        <v>0</v>
-      </c>
-      <c r="E3" s="19">
-        <v>0</v>
-      </c>
-      <c r="F3" s="19">
-        <v>0</v>
-      </c>
-      <c r="G3" s="19">
-        <v>0</v>
-      </c>
-      <c r="H3" s="19">
-        <v>0</v>
-      </c>
-      <c r="I3" s="19">
-        <v>0</v>
-      </c>
-      <c r="J3" s="19">
-        <v>0</v>
-      </c>
-      <c r="K3" s="19">
-        <v>0</v>
-      </c>
-      <c r="L3" s="19">
-        <v>0</v>
-      </c>
-      <c r="M3" s="19">
-        <v>0</v>
-      </c>
-      <c r="N3" s="19">
-        <v>0</v>
-      </c>
-      <c r="O3" s="19">
-        <v>0</v>
-      </c>
-      <c r="P3" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="19">
-        <v>0</v>
-      </c>
-      <c r="R3" s="19">
-        <v>0</v>
-      </c>
-      <c r="S3" s="19">
-        <v>0</v>
-      </c>
-      <c r="T3" s="19">
-        <v>0</v>
-      </c>
-      <c r="U3" s="19">
-        <v>0</v>
-      </c>
-      <c r="V3" s="19">
-        <v>0</v>
-      </c>
-      <c r="W3" s="19">
-        <v>0</v>
-      </c>
-      <c r="X3" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="19">
+      <c r="B3" s="18">
+        <v>0</v>
+      </c>
+      <c r="C3" s="18">
+        <v>0</v>
+      </c>
+      <c r="D3" s="18">
+        <v>0</v>
+      </c>
+      <c r="E3" s="18">
+        <v>0</v>
+      </c>
+      <c r="F3" s="18">
+        <v>0</v>
+      </c>
+      <c r="G3" s="18">
+        <v>0</v>
+      </c>
+      <c r="H3" s="18">
+        <v>0</v>
+      </c>
+      <c r="I3" s="18">
+        <v>0</v>
+      </c>
+      <c r="J3" s="18">
+        <v>0</v>
+      </c>
+      <c r="K3" s="18">
+        <v>0</v>
+      </c>
+      <c r="L3" s="18">
+        <v>0</v>
+      </c>
+      <c r="M3" s="18">
+        <v>0</v>
+      </c>
+      <c r="N3" s="18">
+        <v>0</v>
+      </c>
+      <c r="O3" s="18">
+        <v>0</v>
+      </c>
+      <c r="P3" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="18">
+        <v>0</v>
+      </c>
+      <c r="R3" s="18">
+        <v>0</v>
+      </c>
+      <c r="S3" s="18">
+        <v>0</v>
+      </c>
+      <c r="T3" s="18">
+        <v>0</v>
+      </c>
+      <c r="U3" s="18">
+        <v>0</v>
+      </c>
+      <c r="V3" s="18">
+        <v>0</v>
+      </c>
+      <c r="W3" s="18">
+        <v>0</v>
+      </c>
+      <c r="X3" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="18">
         <v>0</v>
       </c>
     </row>
@@ -10605,94 +12147,94 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="19">
-        <v>0</v>
-      </c>
-      <c r="C4" s="19">
-        <v>0</v>
-      </c>
-      <c r="D4" s="19">
-        <v>0</v>
-      </c>
-      <c r="E4" s="19">
-        <v>0</v>
-      </c>
-      <c r="F4" s="19">
-        <v>0</v>
-      </c>
-      <c r="G4" s="19">
-        <v>0</v>
-      </c>
-      <c r="H4" s="19">
-        <v>0</v>
-      </c>
-      <c r="I4" s="19">
-        <v>0</v>
-      </c>
-      <c r="J4" s="19">
-        <v>0</v>
-      </c>
-      <c r="K4" s="19">
-        <v>0</v>
-      </c>
-      <c r="L4" s="19">
-        <v>0</v>
-      </c>
-      <c r="M4" s="19">
-        <v>0</v>
-      </c>
-      <c r="N4" s="19">
-        <v>0</v>
-      </c>
-      <c r="O4" s="19">
-        <v>0</v>
-      </c>
-      <c r="P4" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="19">
-        <v>0</v>
-      </c>
-      <c r="R4" s="19">
-        <v>0</v>
-      </c>
-      <c r="S4" s="19">
-        <v>0</v>
-      </c>
-      <c r="T4" s="19">
-        <v>0</v>
-      </c>
-      <c r="U4" s="19">
-        <v>0</v>
-      </c>
-      <c r="V4" s="19">
-        <v>0</v>
-      </c>
-      <c r="W4" s="19">
-        <v>0</v>
-      </c>
-      <c r="X4" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="19">
+      <c r="B4" s="18">
+        <v>0</v>
+      </c>
+      <c r="C4" s="18">
+        <v>0</v>
+      </c>
+      <c r="D4" s="18">
+        <v>0</v>
+      </c>
+      <c r="E4" s="18">
+        <v>0</v>
+      </c>
+      <c r="F4" s="18">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18">
+        <v>0</v>
+      </c>
+      <c r="H4" s="18">
+        <v>0</v>
+      </c>
+      <c r="I4" s="18">
+        <v>0</v>
+      </c>
+      <c r="J4" s="18">
+        <v>0</v>
+      </c>
+      <c r="K4" s="18">
+        <v>0</v>
+      </c>
+      <c r="L4" s="18">
+        <v>0</v>
+      </c>
+      <c r="M4" s="18">
+        <v>0</v>
+      </c>
+      <c r="N4" s="18">
+        <v>0</v>
+      </c>
+      <c r="O4" s="18">
+        <v>0</v>
+      </c>
+      <c r="P4" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="18">
+        <v>0</v>
+      </c>
+      <c r="R4" s="18">
+        <v>0</v>
+      </c>
+      <c r="S4" s="18">
+        <v>0</v>
+      </c>
+      <c r="T4" s="18">
+        <v>0</v>
+      </c>
+      <c r="U4" s="18">
+        <v>0</v>
+      </c>
+      <c r="V4" s="18">
+        <v>0</v>
+      </c>
+      <c r="W4" s="18">
+        <v>0</v>
+      </c>
+      <c r="X4" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="18">
         <v>0</v>
       </c>
     </row>
@@ -10700,94 +12242,94 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="19">
-        <v>0</v>
-      </c>
-      <c r="C5" s="19">
-        <v>0</v>
-      </c>
-      <c r="D5" s="19">
-        <v>0</v>
-      </c>
-      <c r="E5" s="19">
-        <v>0</v>
-      </c>
-      <c r="F5" s="19">
-        <v>0</v>
-      </c>
-      <c r="G5" s="19">
-        <v>0</v>
-      </c>
-      <c r="H5" s="19">
-        <v>0</v>
-      </c>
-      <c r="I5" s="19">
-        <v>0</v>
-      </c>
-      <c r="J5" s="19">
-        <v>0</v>
-      </c>
-      <c r="K5" s="19">
-        <v>0</v>
-      </c>
-      <c r="L5" s="19">
-        <v>0</v>
-      </c>
-      <c r="M5" s="19">
-        <v>0</v>
-      </c>
-      <c r="N5" s="19">
-        <v>0</v>
-      </c>
-      <c r="O5" s="19">
-        <v>0</v>
-      </c>
-      <c r="P5" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="19">
-        <v>0</v>
-      </c>
-      <c r="R5" s="19">
-        <v>0</v>
-      </c>
-      <c r="S5" s="19">
-        <v>0</v>
-      </c>
-      <c r="T5" s="19">
-        <v>0</v>
-      </c>
-      <c r="U5" s="19">
-        <v>0</v>
-      </c>
-      <c r="V5" s="19">
-        <v>0</v>
-      </c>
-      <c r="W5" s="19">
-        <v>0</v>
-      </c>
-      <c r="X5" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="19">
+      <c r="B5" s="18">
+        <v>0</v>
+      </c>
+      <c r="C5" s="18">
+        <v>0</v>
+      </c>
+      <c r="D5" s="18">
+        <v>0</v>
+      </c>
+      <c r="E5" s="18">
+        <v>0</v>
+      </c>
+      <c r="F5" s="18">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18">
+        <v>0</v>
+      </c>
+      <c r="I5" s="18">
+        <v>0</v>
+      </c>
+      <c r="J5" s="18">
+        <v>0</v>
+      </c>
+      <c r="K5" s="18">
+        <v>0</v>
+      </c>
+      <c r="L5" s="18">
+        <v>0</v>
+      </c>
+      <c r="M5" s="18">
+        <v>0</v>
+      </c>
+      <c r="N5" s="18">
+        <v>0</v>
+      </c>
+      <c r="O5" s="18">
+        <v>0</v>
+      </c>
+      <c r="P5" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="18">
+        <v>0</v>
+      </c>
+      <c r="R5" s="18">
+        <v>0</v>
+      </c>
+      <c r="S5" s="18">
+        <v>0</v>
+      </c>
+      <c r="T5" s="18">
+        <v>0</v>
+      </c>
+      <c r="U5" s="18">
+        <v>0</v>
+      </c>
+      <c r="V5" s="18">
+        <v>0</v>
+      </c>
+      <c r="W5" s="18">
+        <v>0</v>
+      </c>
+      <c r="X5" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="18">
         <v>0</v>
       </c>
     </row>
@@ -10795,219 +12337,219 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="19">
-        <f>'Passenger Vehicle Calculations'!C47</f>
-        <v>7252.8733459787563</v>
-      </c>
-      <c r="C6" s="19">
-        <f>'Passenger Vehicle Calculations'!D47</f>
-        <v>4193.501468133536</v>
-      </c>
-      <c r="D6" s="19">
-        <f>'Passenger Vehicle Calculations'!E47</f>
-        <v>2371.7262681335355</v>
-      </c>
-      <c r="E6" s="19">
-        <f>'Passenger Vehicle Calculations'!F47</f>
-        <v>2329.8343100151742</v>
-      </c>
-      <c r="F6" s="19">
-        <f>'Passenger Vehicle Calculations'!G47</f>
-        <v>1671.1026100151744</v>
-      </c>
-      <c r="G6" s="19">
-        <f>'Passenger Vehicle Calculations'!H47</f>
-        <v>1625.6076100151745</v>
-      </c>
-      <c r="H6" s="19">
-        <f>'Passenger Vehicle Calculations'!I47</f>
-        <v>1591.1151100151747</v>
-      </c>
-      <c r="I6" s="19">
-        <f>'Passenger Vehicle Calculations'!J47</f>
-        <v>1593.1401100151747</v>
-      </c>
-      <c r="J6" s="19">
-        <f>'Passenger Vehicle Calculations'!K47</f>
-        <v>1599.8726100151744</v>
-      </c>
-      <c r="K6" s="19">
-        <f>'Passenger Vehicle Calculations'!L47</f>
-        <v>1658.1326100151746</v>
-      </c>
-      <c r="L6" s="19">
-        <f>'Passenger Vehicle Calculations'!M47</f>
-        <v>1713.9176100151744</v>
-      </c>
-      <c r="M6" s="19">
-        <f>'Passenger Vehicle Calculations'!N47</f>
-        <v>1724.7001100151747</v>
-      </c>
-      <c r="N6" s="19">
-        <f>'Passenger Vehicle Calculations'!O47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="O6" s="19">
-        <f>'Passenger Vehicle Calculations'!P47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P6" s="19">
-        <f>'Passenger Vehicle Calculations'!Q47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q6" s="19">
-        <f>'Passenger Vehicle Calculations'!R47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R6" s="19">
-        <f>'Passenger Vehicle Calculations'!S47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S6" s="19">
-        <f>'Passenger Vehicle Calculations'!T47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T6" s="19">
-        <f>'Passenger Vehicle Calculations'!U47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U6" s="19">
-        <f>'Passenger Vehicle Calculations'!V47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V6" s="19">
-        <f>'Passenger Vehicle Calculations'!W47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W6" s="19">
-        <f>'Passenger Vehicle Calculations'!X47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X6" s="19">
-        <f>'Passenger Vehicle Calculations'!Y47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y6" s="19">
-        <f>'Passenger Vehicle Calculations'!Z47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z6" s="19">
-        <f>'Passenger Vehicle Calculations'!AA47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA6" s="19">
-        <f>'Passenger Vehicle Calculations'!AB47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB6" s="19">
-        <f>'Passenger Vehicle Calculations'!AC47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC6" s="19">
-        <f>'Passenger Vehicle Calculations'!AD47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD6" s="19">
-        <f>'Passenger Vehicle Calculations'!AE47</f>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE6" s="19">
-        <f>'Passenger Vehicle Calculations'!AF47</f>
-        <v>568.32511001517457</v>
+      <c r="B6" s="18">
+        <f>'Passenger Vehicle Calculations'!C69</f>
+        <v>6868.4402011018146</v>
+      </c>
+      <c r="C6" s="18">
+        <f>'Passenger Vehicle Calculations'!D69</f>
+        <v>3805.0788061456087</v>
+      </c>
+      <c r="D6" s="18">
+        <f>'Passenger Vehicle Calculations'!E69</f>
+        <v>3662.355308727233</v>
+      </c>
+      <c r="E6" s="18">
+        <f>'Passenger Vehicle Calculations'!F69</f>
+        <v>2999.2858045496764</v>
+      </c>
+      <c r="F6" s="18">
+        <f>'Passenger Vehicle Calculations'!G69</f>
+        <v>2492.4252043210045</v>
+      </c>
+      <c r="G6" s="18">
+        <f>'Passenger Vehicle Calculations'!H69</f>
+        <v>2355.6859555808901</v>
+      </c>
+      <c r="H6" s="18">
+        <f>'Passenger Vehicle Calculations'!I69</f>
+        <v>2224.0661798520518</v>
+      </c>
+      <c r="I6" s="18">
+        <f>'Passenger Vehicle Calculations'!J69</f>
+        <v>2167.4924466149887</v>
+      </c>
+      <c r="J6" s="18">
+        <f>'Passenger Vehicle Calculations'!K69</f>
+        <v>2112.6190346880921</v>
+      </c>
+      <c r="K6" s="18">
+        <f>'Passenger Vehicle Calculations'!L69</f>
+        <v>2059.3856145068316</v>
+      </c>
+      <c r="L6" s="18">
+        <f>'Passenger Vehicle Calculations'!M69</f>
+        <v>2006.7216198707158</v>
+      </c>
+      <c r="M6" s="18">
+        <f>'Passenger Vehicle Calculations'!N69</f>
+        <v>1955.3640812230597</v>
+      </c>
+      <c r="N6" s="18">
+        <f>'Passenger Vehicle Calculations'!O69</f>
+        <v>75.947919361469985</v>
+      </c>
+      <c r="O6" s="18">
+        <f>'Passenger Vehicle Calculations'!P69</f>
+        <v>73.735844040262123</v>
+      </c>
+      <c r="P6" s="18">
+        <f>'Passenger Vehicle Calculations'!Q69</f>
+        <v>71.588198097341873</v>
+      </c>
+      <c r="Q6" s="18">
+        <f>'Passenger Vehicle Calculations'!R69</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="18">
+        <f>'Passenger Vehicle Calculations'!S69</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="18">
+        <f>'Passenger Vehicle Calculations'!T69</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="18">
+        <f>'Passenger Vehicle Calculations'!U69</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="18">
+        <f>'Passenger Vehicle Calculations'!V69</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="18">
+        <f>'Passenger Vehicle Calculations'!W69</f>
+        <v>0</v>
+      </c>
+      <c r="W6" s="18">
+        <f>'Passenger Vehicle Calculations'!X69</f>
+        <v>0</v>
+      </c>
+      <c r="X6" s="18">
+        <f>'Passenger Vehicle Calculations'!Y69</f>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="18">
+        <f>'Passenger Vehicle Calculations'!Z69</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="18">
+        <f>'Passenger Vehicle Calculations'!AA69</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="18">
+        <f>'Passenger Vehicle Calculations'!AB69</f>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="18">
+        <f>'Passenger Vehicle Calculations'!AC69</f>
+        <v>0</v>
+      </c>
+      <c r="AC6" s="18">
+        <f>'Passenger Vehicle Calculations'!AD69</f>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="18">
+        <f>'Passenger Vehicle Calculations'!AE69</f>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="18">
+        <f>'Passenger Vehicle Calculations'!AF69</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="19">
-        <v>0</v>
-      </c>
-      <c r="C7" s="19">
-        <v>0</v>
-      </c>
-      <c r="D7" s="19">
-        <v>0</v>
-      </c>
-      <c r="E7" s="19">
-        <v>0</v>
-      </c>
-      <c r="F7" s="19">
-        <v>0</v>
-      </c>
-      <c r="G7" s="19">
-        <v>0</v>
-      </c>
-      <c r="H7" s="19">
-        <v>0</v>
-      </c>
-      <c r="I7" s="19">
-        <v>0</v>
-      </c>
-      <c r="J7" s="19">
-        <v>0</v>
-      </c>
-      <c r="K7" s="19">
-        <v>0</v>
-      </c>
-      <c r="L7" s="19">
-        <v>0</v>
-      </c>
-      <c r="M7" s="19">
-        <v>0</v>
-      </c>
-      <c r="N7" s="19">
-        <v>0</v>
-      </c>
-      <c r="O7" s="19">
-        <v>0</v>
-      </c>
-      <c r="P7" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="19">
-        <v>0</v>
-      </c>
-      <c r="R7" s="19">
-        <v>0</v>
-      </c>
-      <c r="S7" s="19">
-        <v>0</v>
-      </c>
-      <c r="T7" s="19">
-        <v>0</v>
-      </c>
-      <c r="U7" s="19">
-        <v>0</v>
-      </c>
-      <c r="V7" s="19">
-        <v>0</v>
-      </c>
-      <c r="W7" s="19">
-        <v>0</v>
-      </c>
-      <c r="X7" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="19">
+      <c r="B7" s="18">
+        <v>0</v>
+      </c>
+      <c r="C7" s="18">
+        <v>0</v>
+      </c>
+      <c r="D7" s="18">
+        <v>0</v>
+      </c>
+      <c r="E7" s="18">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18">
+        <v>0</v>
+      </c>
+      <c r="H7" s="18">
+        <v>0</v>
+      </c>
+      <c r="I7" s="18">
+        <v>0</v>
+      </c>
+      <c r="J7" s="18">
+        <v>0</v>
+      </c>
+      <c r="K7" s="18">
+        <v>0</v>
+      </c>
+      <c r="L7" s="18">
+        <v>0</v>
+      </c>
+      <c r="M7" s="18">
+        <v>0</v>
+      </c>
+      <c r="N7" s="18">
+        <v>0</v>
+      </c>
+      <c r="O7" s="18">
+        <v>0</v>
+      </c>
+      <c r="P7" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>0</v>
+      </c>
+      <c r="R7" s="18">
+        <v>0</v>
+      </c>
+      <c r="S7" s="18">
+        <v>0</v>
+      </c>
+      <c r="T7" s="18">
+        <v>0</v>
+      </c>
+      <c r="U7" s="18">
+        <v>0</v>
+      </c>
+      <c r="V7" s="18">
+        <v>0</v>
+      </c>
+      <c r="W7" s="18">
+        <v>0</v>
+      </c>
+      <c r="X7" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="18">
         <v>0</v>
       </c>
     </row>
@@ -11015,123 +12557,123 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="19">
-        <v>0</v>
-      </c>
-      <c r="C8" s="19">
-        <v>0</v>
-      </c>
-      <c r="D8" s="19">
+      <c r="B8" s="18">
+        <v>0</v>
+      </c>
+      <c r="C8" s="18">
+        <v>0</v>
+      </c>
+      <c r="D8" s="18">
         <f>D2</f>
-        <v>2371.7262681335355</v>
-      </c>
-      <c r="E8" s="19">
+        <v>5130.1015918271351</v>
+      </c>
+      <c r="E8" s="18">
         <f t="shared" ref="E8:AE8" si="0">E2</f>
-        <v>2329.8343100151742</v>
-      </c>
-      <c r="F8" s="19">
+        <v>3819.9265877142789</v>
+      </c>
+      <c r="F8" s="18">
         <f t="shared" si="0"/>
-        <v>1671.1026100151744</v>
-      </c>
-      <c r="G8" s="19">
+        <v>3565.6148024975096</v>
+      </c>
+      <c r="G8" s="18">
         <f t="shared" si="0"/>
-        <v>1625.6076100151745</v>
-      </c>
-      <c r="H8" s="19">
+        <v>3312.3286898445285</v>
+      </c>
+      <c r="H8" s="18">
         <f t="shared" si="0"/>
-        <v>1591.1151100151747</v>
-      </c>
-      <c r="I8" s="19">
+        <v>2579.6280722494112</v>
+      </c>
+      <c r="I8" s="18">
         <f t="shared" si="0"/>
-        <v>1593.1401100151747</v>
-      </c>
-      <c r="J8" s="19">
+        <v>2607.4715657030551</v>
+      </c>
+      <c r="J8" s="18">
         <f t="shared" si="0"/>
-        <v>1599.8726100151744</v>
-      </c>
-      <c r="K8" s="19">
+        <v>2637.5199855509622</v>
+      </c>
+      <c r="K8" s="18">
         <f t="shared" si="0"/>
-        <v>1658.1326100151746</v>
-      </c>
-      <c r="L8" s="19">
+        <v>2669.5709726607206</v>
+      </c>
+      <c r="L8" s="18">
         <f t="shared" si="0"/>
-        <v>1713.9176100151744</v>
-      </c>
-      <c r="M8" s="19">
+        <v>2692.8330628056278</v>
+      </c>
+      <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>1724.7001100151747</v>
-      </c>
-      <c r="N8" s="19">
+        <v>2715.0603144269971</v>
+      </c>
+      <c r="N8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="O8" s="19">
+        <v>157.82432189025366</v>
+      </c>
+      <c r="O8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="P8" s="19">
+        <v>153.22749698082879</v>
+      </c>
+      <c r="P8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Q8" s="19">
+        <v>148.76456017556194</v>
+      </c>
+      <c r="Q8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="R8" s="19">
+        <v>0</v>
+      </c>
+      <c r="R8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="S8" s="19">
+        <v>0</v>
+      </c>
+      <c r="S8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="T8" s="19">
+        <v>0</v>
+      </c>
+      <c r="T8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="U8" s="19">
+        <v>0</v>
+      </c>
+      <c r="U8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="V8" s="19">
+        <v>0</v>
+      </c>
+      <c r="V8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="W8" s="19">
+        <v>0</v>
+      </c>
+      <c r="W8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="X8" s="19">
+        <v>0</v>
+      </c>
+      <c r="X8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Y8" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="Z8" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AA8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AB8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AC8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AD8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
-      </c>
-      <c r="AE8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="18">
         <f t="shared" si="0"/>
-        <v>568.32511001517457</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11149,6 +12691,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.35">
@@ -11256,45 +12799,45 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="E2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="F2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="G2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="H2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="I2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="J2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="K2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="L2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
-      </c>
-      <c r="M2">
-        <f>'Commercial Vehicles'!$B$7</f>
-        <v>27004</v>
+      <c r="D2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!C14*'Commercial Vehicles'!$B16</f>
+        <v>25920.517751770582</v>
+      </c>
+      <c r="E2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!D14*'Commercial Vehicles'!$B16</f>
+        <v>25177.910605727324</v>
+      </c>
+      <c r="F2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!E14*'Commercial Vehicles'!$B16</f>
+        <v>24444.57340361876</v>
+      </c>
+      <c r="G2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!F14*'Commercial Vehicles'!$B16</f>
+        <v>23732.59553749394</v>
+      </c>
+      <c r="H2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!G14*'Commercial Vehicles'!$B16</f>
+        <v>23041.354890770817</v>
+      </c>
+      <c r="I2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!H14*'Commercial Vehicles'!$B16</f>
+        <v>22370.247466767789</v>
+      </c>
+      <c r="J2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!I14*'Commercial Vehicles'!$B16</f>
+        <v>21718.686860939597</v>
+      </c>
+      <c r="K2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!J14*'Commercial Vehicles'!$B16</f>
+        <v>21086.103748485046</v>
+      </c>
+      <c r="L2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!K14*'Commercial Vehicles'!$B16</f>
+        <v>20471.945386878688</v>
+      </c>
+      <c r="M2" s="51">
+        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!L14*'Commercial Vehicles'!$B16</f>
+        <v>19875.675132891927</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -11648,43 +13191,43 @@
       </c>
       <c r="D6">
         <f>D2</f>
-        <v>27004</v>
+        <v>25920.517751770582</v>
       </c>
       <c r="E6">
         <f t="shared" ref="E6:M6" si="0">E2</f>
-        <v>27004</v>
+        <v>25177.910605727324</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>24444.57340361876</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>23732.59553749394</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>23041.354890770817</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>22370.247466767789</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>21718.686860939597</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>21086.103748485046</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>20471.945386878688</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>27004</v>
+        <v>19875.675132891927</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -11848,43 +13391,43 @@
       </c>
       <c r="D8">
         <f>D2</f>
-        <v>27004</v>
+        <v>25920.517751770582</v>
       </c>
       <c r="E8">
         <f t="shared" ref="E8:M8" si="1">E2</f>
-        <v>27004</v>
+        <v>25177.910605727324</v>
       </c>
       <c r="F8">
         <f t="shared" si="1"/>
-        <v>27004</v>
+        <v>24444.57340361876</v>
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>27004</v>
+        <v>23732.59553749394</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>27004</v>
+        <v>23041.354890770817</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>27004</v>
+        <v>22370.247466767789</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>27004</v>
+        <v>21718.686860939597</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>27004</v>
+        <v>21086.103748485046</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>27004</v>
+        <v>20471.945386878688</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>27004</v>
+        <v>19875.675132891927</v>
       </c>
       <c r="N8">
         <v>0</v>

--- a/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
+++ b/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\trans\BVS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\BVS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E25C66-036F-474A-A81B-895765D51030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72764887-92EB-4105-8C57-DAC59B97E0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8835" yWindow="360" windowWidth="20295" windowHeight="12150" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="BVS-psgr-LDVs" sheetId="2" r:id="rId5"/>
     <sheet name="BVS-psgr-HDVs" sheetId="101" r:id="rId6"/>
     <sheet name="BVS-psgr-aircraft" sheetId="105" r:id="rId7"/>
-    <sheet name="BVP-psgr-rail" sheetId="104" r:id="rId8"/>
+    <sheet name="BVS-psgr-rail" sheetId="104" r:id="rId8"/>
     <sheet name="BVS-psgr-ships" sheetId="103" r:id="rId9"/>
     <sheet name="BVS-psgr-motorbikes" sheetId="102" r:id="rId10"/>
     <sheet name="frgt" sheetId="106" r:id="rId11"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="124">
   <si>
     <t>Sources:</t>
   </si>
@@ -515,6 +515,9 @@
   <si>
     <t>Frgt LDV (2012 $)</t>
   </si>
+  <si>
+    <t>took out IRA</t>
+  </si>
 </sst>
 </file>
 
@@ -526,7 +529,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="m\-d"/>
-    <numFmt numFmtId="172" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -668,7 +671,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -702,6 +705,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -827,7 +836,7 @@
     <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -897,9 +906,10 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="33" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="12" fillId="0" borderId="0" xfId="31" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="31" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="31" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="34">
     <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2289,32 +2299,25 @@
         <v>9098.157067904207</v>
       </c>
       <c r="G2">
-        <f>'Commercial Vehicles'!E10</f>
-        <v>8900.5394373583313</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <f>'Commercial Vehicles'!F10</f>
-        <v>8762.1955571514172</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <f>'Commercial Vehicles'!G10</f>
-        <v>8574.638599520662</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <f>'Commercial Vehicles'!H10</f>
-        <v>8327.2183891071436</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <f>'Commercial Vehicles'!I10</f>
-        <v>8038.2687173078502</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <f>'Commercial Vehicles'!J10</f>
-        <v>7772.0490463949827</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <f>'Commercial Vehicles'!K10</f>
-        <v>7566.1942040579743</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -2680,31 +2683,31 @@
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>8900.5394373583313</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>8762.1955571514172</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>8574.638599520662</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>8327.2183891071436</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>8038.2687173078502</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>7772.0490463949827</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>7566.1942040579743</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2880,31 +2883,31 @@
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>8900.5394373583313</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>8762.1955571514172</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>8574.638599520662</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>8327.2183891071436</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>8038.2687173078502</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>7772.0490463949827</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>7566.1942040579743</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3097,85 +3100,78 @@
         <v>28423.922562347398</v>
       </c>
       <c r="G2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!F14</f>
-        <v>27596.041322667374</v>
+        <v>0</v>
       </c>
       <c r="H2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!G14</f>
-        <v>26792.273128803277</v>
+        <v>0</v>
       </c>
       <c r="I2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!H14</f>
-        <v>26011.915659032311</v>
+        <v>0</v>
       </c>
       <c r="J2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!I14</f>
-        <v>25254.287047604183</v>
+        <v>0</v>
       </c>
       <c r="K2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!J14</f>
-        <v>24518.725288936101</v>
+        <v>0</v>
       </c>
       <c r="L2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!K14</f>
-        <v>23804.587659161265</v>
+        <v>0</v>
       </c>
       <c r="M2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!L14</f>
-        <v>23111.250154525496</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="51">
+        <v>0</v>
+      </c>
+      <c r="O2" s="51">
+        <v>0</v>
+      </c>
+      <c r="P2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="51">
+        <v>0</v>
+      </c>
+      <c r="R2" s="51">
+        <v>0</v>
+      </c>
+      <c r="S2" s="51">
+        <v>0</v>
+      </c>
+      <c r="T2" s="51">
+        <v>0</v>
+      </c>
+      <c r="U2" s="51">
+        <v>0</v>
+      </c>
+      <c r="V2" s="51">
+        <v>0</v>
+      </c>
+      <c r="W2" s="51">
+        <v>0</v>
+      </c>
+      <c r="X2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="51">
         <v>0</v>
       </c>
     </row>
@@ -3488,31 +3484,31 @@
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>27596.041322667374</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>26792.273128803277</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>26011.915659032311</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>25254.287047604183</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>24518.725288936101</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>23804.587659161265</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>23111.250154525496</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3688,31 +3684,31 @@
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>27596.041322667374</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>26792.273128803277</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>26011.915659032311</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>25254.287047604183</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>24518.725288936101</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>23804.587659161265</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>23111.250154525496</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -8939,6 +8935,9 @@
       <c r="A66" s="5" t="s">
         <v>39</v>
       </c>
+      <c r="H66" s="52" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="C67">
@@ -9038,11 +9037,11 @@
       </c>
       <c r="B68" s="5"/>
       <c r="C68" s="5">
-        <f t="shared" ref="C68:AF68" si="8">B5+C63</f>
+        <f>B5+C63</f>
         <v>1930.7404811231229</v>
       </c>
       <c r="D68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="D68:G68" si="8">C5+D63</f>
         <v>1599.8025784220101</v>
       </c>
       <c r="E68" s="5">
@@ -9050,7 +9049,7 @@
         <v>5130.1015918271351</v>
       </c>
       <c r="F68" s="5">
-        <f t="shared" si="8"/>
+        <f>E5+F63</f>
         <v>3819.9265877142789</v>
       </c>
       <c r="G68" s="5">
@@ -9058,103 +9057,103 @@
         <v>3565.6148024975096</v>
       </c>
       <c r="H68" s="5">
-        <f t="shared" si="8"/>
-        <v>3312.3286898445285</v>
+        <f>H63</f>
+        <v>194.10400882122519</v>
       </c>
       <c r="I68" s="5">
-        <f t="shared" si="8"/>
-        <v>2579.6280722494112</v>
+        <f t="shared" ref="I68:AF68" si="9">I63</f>
+        <v>188.4504940011895</v>
       </c>
       <c r="J68" s="5">
-        <f t="shared" si="8"/>
-        <v>2607.4715657030551</v>
+        <f t="shared" si="9"/>
+        <v>182.96164466134903</v>
       </c>
       <c r="K68" s="5">
-        <f t="shared" si="8"/>
-        <v>2637.5199855509622</v>
+        <f t="shared" si="9"/>
+        <v>177.63266471975632</v>
       </c>
       <c r="L68" s="5">
-        <f t="shared" si="8"/>
-        <v>2669.5709726607206</v>
+        <f t="shared" si="9"/>
+        <v>172.45889778617118</v>
       </c>
       <c r="M68" s="5">
-        <f t="shared" si="8"/>
-        <v>2692.8330628056278</v>
+        <f t="shared" si="9"/>
+        <v>167.43582309337009</v>
       </c>
       <c r="N68" s="5">
-        <f t="shared" si="8"/>
-        <v>2715.0603144269971</v>
+        <f t="shared" si="9"/>
+        <v>162.55905154696123</v>
       </c>
       <c r="O68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>157.82432189025366</v>
       </c>
       <c r="P68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>153.22749698082879</v>
       </c>
       <c r="Q68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>148.76456017556194</v>
       </c>
       <c r="R68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AC68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF68" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -9167,119 +9166,119 @@
         <v>6868.4402011018146</v>
       </c>
       <c r="D69" s="5">
-        <f t="shared" ref="D69:AF69" si="9">C6+D64</f>
+        <f t="shared" ref="D69:G69" si="10">C6+D64</f>
         <v>3805.0788061456087</v>
       </c>
       <c r="E69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3662.355308727233</v>
       </c>
       <c r="F69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2999.2858045496764</v>
       </c>
       <c r="G69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2492.4252043210045</v>
       </c>
       <c r="H69" s="5">
-        <f t="shared" si="9"/>
-        <v>2355.6859555808901</v>
+        <f>H64</f>
+        <v>93.406361156067433</v>
       </c>
       <c r="I69" s="5">
-        <f t="shared" si="9"/>
-        <v>2224.0661798520518</v>
+        <f t="shared" ref="I69:AF69" si="11">I64</f>
+        <v>90.685787530162571</v>
       </c>
       <c r="J69" s="5">
-        <f t="shared" si="9"/>
-        <v>2167.4924466149887</v>
+        <f t="shared" si="11"/>
+        <v>88.04445391277919</v>
       </c>
       <c r="K69" s="5">
-        <f t="shared" si="9"/>
-        <v>2112.6190346880921</v>
+        <f t="shared" si="11"/>
+        <v>85.480052342504052</v>
       </c>
       <c r="L69" s="5">
-        <f t="shared" si="9"/>
-        <v>2059.3856145068316</v>
+        <f t="shared" si="11"/>
+        <v>82.990342080101016</v>
       </c>
       <c r="M69" s="5">
-        <f t="shared" si="9"/>
-        <v>2006.7216198707158</v>
+        <f t="shared" si="11"/>
+        <v>80.573147650583522</v>
       </c>
       <c r="N69" s="5">
-        <f t="shared" si="9"/>
-        <v>1955.3640812230597</v>
+        <f t="shared" si="11"/>
+        <v>78.226356942314084</v>
       </c>
       <c r="O69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>75.947919361469985</v>
       </c>
       <c r="P69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>73.735844040262123</v>
       </c>
       <c r="Q69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>71.588198097341873</v>
       </c>
       <c r="R69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="S69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="U69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="W69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="X69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Y69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Z69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AA69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AB69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AD69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AF69" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -9839,11 +9838,11 @@
         <v>332.79266010000003</v>
       </c>
       <c r="F98" s="16">
-        <f t="shared" ref="F98:F107" si="10">G$82</f>
+        <f t="shared" ref="F98:F107" si="12">G$82</f>
         <v>0.03</v>
       </c>
       <c r="G98" s="22">
-        <f t="shared" ref="G98:G107" si="11">D$84/D98</f>
+        <f t="shared" ref="G98:G107" si="13">D$84/D98</f>
         <v>0.68990103306668438</v>
       </c>
     </row>
@@ -9852,15 +9851,15 @@
         <v>2027</v>
       </c>
       <c r="D99">
-        <f t="shared" ref="D99:D107" si="12">D98*(1+F99)</f>
+        <f t="shared" ref="D99:D107" si="14">D98*(1+F99)</f>
         <v>342.77643990300004</v>
       </c>
       <c r="F99" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.03</v>
       </c>
       <c r="G99" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.66980682822008197</v>
       </c>
     </row>
@@ -9869,15 +9868,15 @@
         <v>2028</v>
       </c>
       <c r="D100">
+        <f t="shared" si="14"/>
+        <v>353.05973310009006</v>
+      </c>
+      <c r="F100" s="16">
         <f t="shared" si="12"/>
-        <v>353.05973310009006</v>
-      </c>
-      <c r="F100" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G100" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.65029789147580774</v>
       </c>
     </row>
@@ -9886,15 +9885,15 @@
         <v>2029</v>
       </c>
       <c r="D101">
+        <f t="shared" si="14"/>
+        <v>363.65152509309274</v>
+      </c>
+      <c r="F101" s="16">
         <f t="shared" si="12"/>
-        <v>363.65152509309274</v>
-      </c>
-      <c r="F101" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G101" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.63135717619010456</v>
       </c>
     </row>
@@ -9903,15 +9902,15 @@
         <v>2030</v>
       </c>
       <c r="D102">
+        <f t="shared" si="14"/>
+        <v>374.56107084588552</v>
+      </c>
+      <c r="F102" s="16">
         <f t="shared" si="12"/>
-        <v>374.56107084588552</v>
-      </c>
-      <c r="F102" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G102" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.61296813222340252</v>
       </c>
     </row>
@@ -9920,15 +9919,15 @@
         <v>2031</v>
       </c>
       <c r="D103">
+        <f t="shared" si="14"/>
+        <v>385.79790297126209</v>
+      </c>
+      <c r="F103" s="16">
         <f t="shared" si="12"/>
-        <v>385.79790297126209</v>
-      </c>
-      <c r="F103" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G103" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.59511469147903162</v>
       </c>
     </row>
@@ -9937,15 +9936,15 @@
         <v>2032</v>
       </c>
       <c r="D104">
+        <f t="shared" si="14"/>
+        <v>397.37184006039996</v>
+      </c>
+      <c r="F104" s="16">
         <f t="shared" si="12"/>
-        <v>397.37184006039996</v>
-      </c>
-      <c r="F104" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G104" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.57778125386313739</v>
       </c>
     </row>
@@ -9954,15 +9953,15 @@
         <v>2033</v>
       </c>
       <c r="D105">
+        <f t="shared" si="14"/>
+        <v>409.29299526221195</v>
+      </c>
+      <c r="F105" s="16">
         <f t="shared" si="12"/>
-        <v>409.29299526221195</v>
-      </c>
-      <c r="F105" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G105" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.56095267365353152</v>
       </c>
     </row>
@@ -9971,15 +9970,15 @@
         <v>2034</v>
       </c>
       <c r="D106">
+        <f t="shared" si="14"/>
+        <v>421.57178512007829</v>
+      </c>
+      <c r="F106" s="16">
         <f t="shared" si="12"/>
-        <v>421.57178512007829</v>
-      </c>
-      <c r="F106" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G106" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.54461424626556454</v>
       </c>
     </row>
@@ -9988,15 +9987,15 @@
         <v>2035</v>
       </c>
       <c r="D107">
+        <f t="shared" si="14"/>
+        <v>434.21893867368067</v>
+      </c>
+      <c r="F107" s="16">
         <f t="shared" si="12"/>
-        <v>434.21893867368067</v>
-      </c>
-      <c r="F107" s="16">
-        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="G107" s="22">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.52875169540346068</v>
       </c>
     </row>
@@ -10313,11 +10312,11 @@
         <v>72</v>
       </c>
       <c r="B8" s="26">
-        <f>$B4*$B$16*C$14</f>
+        <f t="shared" ref="B8:K8" si="0">$B4*$B$16*C$14</f>
         <v>25920.517751770582</v>
       </c>
       <c r="C8" s="26">
-        <f>$B4*$B$16*D$14</f>
+        <f t="shared" si="0"/>
         <v>25177.910605727324</v>
       </c>
       <c r="D8" s="26">
@@ -10329,27 +10328,27 @@
         <v>23732.595537493944</v>
       </c>
       <c r="F8" s="26">
-        <f>$B4*$B$16*G$14</f>
+        <f t="shared" si="0"/>
         <v>23041.354890770821</v>
       </c>
       <c r="G8" s="26">
-        <f>$B4*$B$16*H$14</f>
+        <f t="shared" si="0"/>
         <v>22370.247466767785</v>
       </c>
       <c r="H8" s="26">
-        <f>$B4*$B$16*I$14</f>
+        <f t="shared" si="0"/>
         <v>21718.686860939597</v>
       </c>
       <c r="I8" s="26">
-        <f>$B4*$B$16*J$14</f>
+        <f t="shared" si="0"/>
         <v>21086.103748485046</v>
       </c>
       <c r="J8" s="26">
-        <f>$B4*$B$16*K$14</f>
+        <f t="shared" si="0"/>
         <v>20471.945386878688</v>
       </c>
       <c r="K8" s="26">
-        <f>$B4*$B$16*L$14</f>
+        <f t="shared" si="0"/>
         <v>19875.675132891927</v>
       </c>
     </row>
@@ -10362,39 +10361,39 @@
         <v>30140.136920663466</v>
       </c>
       <c r="C9" s="26">
-        <f t="shared" ref="C9:K9" si="0">$B$4*D14</f>
+        <f t="shared" ref="C9:K9" si="1">$B$4*D14</f>
         <v>29276.640239217821</v>
       </c>
       <c r="D9" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28423.922562347398</v>
       </c>
       <c r="E9" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>27596.041322667374</v>
       </c>
       <c r="F9" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26792.273128803277</v>
       </c>
       <c r="G9" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26011.915659032311</v>
       </c>
       <c r="H9" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25254.287047604183</v>
       </c>
       <c r="I9" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24518.725288936101</v>
       </c>
       <c r="J9" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23804.587659161265</v>
       </c>
       <c r="K9" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23111.250154525496</v>
       </c>
     </row>
@@ -10407,39 +10406,39 @@
         <v>9715.0710076103514</v>
       </c>
       <c r="C10" s="35">
-        <f t="shared" ref="C10:K10" si="1">D36</f>
+        <f t="shared" ref="C10:K10" si="2">D36</f>
         <v>9379.5012804435319</v>
       </c>
       <c r="D10" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9098.157067904207</v>
       </c>
       <c r="E10" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8900.5394373583313</v>
       </c>
       <c r="F10" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8762.1955571514172</v>
       </c>
       <c r="G10" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8574.638599520662</v>
       </c>
       <c r="H10" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8327.2183891071436</v>
       </c>
       <c r="I10" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8038.2687173078502</v>
       </c>
       <c r="J10" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7772.0490463949827</v>
       </c>
       <c r="K10" s="35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7566.1942040579743</v>
       </c>
     </row>
@@ -10996,7 +10995,7 @@
         <v>68</v>
       </c>
       <c r="B36" s="26">
-        <f t="shared" ref="B36:AD36" si="2">SUMPRODUCT(B32:B34,$D$23:$D$25)/SUM(B32:B34)</f>
+        <f t="shared" ref="B36" si="3">SUMPRODUCT(B32:B34,$D$23:$D$25)/SUM(B32:B34)</f>
         <v>10128.764188673933</v>
       </c>
       <c r="C36" s="26">
@@ -11004,39 +11003,39 @@
         <v>9715.0710076103514</v>
       </c>
       <c r="D36" s="26">
-        <f t="shared" ref="D36:L36" si="3">SUMPRODUCT(D32:D34,$D$23:$D$25)/SUM(D32:D34)*D14/$B$14</f>
+        <f t="shared" ref="D36:L36" si="4">SUMPRODUCT(D32:D34,$D$23:$D$25)/SUM(D32:D34)*D14/$B$14</f>
         <v>9379.5012804435319</v>
       </c>
       <c r="E36" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9098.157067904207</v>
       </c>
       <c r="F36" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8900.5394373583313</v>
       </c>
       <c r="G36" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8762.1955571514172</v>
       </c>
       <c r="H36" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8574.638599520662</v>
       </c>
       <c r="I36" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8327.2183891071436</v>
       </c>
       <c r="J36" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8038.2687173078502</v>
       </c>
       <c r="K36" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7772.0490463949827</v>
       </c>
       <c r="L36" s="26">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7566.1942040579743</v>
       </c>
       <c r="M36" s="26"/>
@@ -11949,31 +11948,31 @@
       </c>
       <c r="G2" s="18">
         <f>'Passenger Vehicle Calculations'!H68</f>
-        <v>3312.3286898445285</v>
+        <v>194.10400882122519</v>
       </c>
       <c r="H2" s="18">
         <f>'Passenger Vehicle Calculations'!I68</f>
-        <v>2579.6280722494112</v>
+        <v>188.4504940011895</v>
       </c>
       <c r="I2" s="18">
         <f>'Passenger Vehicle Calculations'!J68</f>
-        <v>2607.4715657030551</v>
+        <v>182.96164466134903</v>
       </c>
       <c r="J2" s="18">
         <f>'Passenger Vehicle Calculations'!K68</f>
-        <v>2637.5199855509622</v>
+        <v>177.63266471975632</v>
       </c>
       <c r="K2" s="18">
         <f>'Passenger Vehicle Calculations'!L68</f>
-        <v>2669.5709726607206</v>
+        <v>172.45889778617118</v>
       </c>
       <c r="L2" s="18">
         <f>'Passenger Vehicle Calculations'!M68</f>
-        <v>2692.8330628056278</v>
+        <v>167.43582309337009</v>
       </c>
       <c r="M2" s="18">
         <f>'Passenger Vehicle Calculations'!N68</f>
-        <v>2715.0603144269971</v>
+        <v>162.55905154696123</v>
       </c>
       <c r="N2" s="18">
         <f>'Passenger Vehicle Calculations'!O68</f>
@@ -12359,31 +12358,31 @@
       </c>
       <c r="G6" s="18">
         <f>'Passenger Vehicle Calculations'!H69</f>
-        <v>2355.6859555808901</v>
+        <v>93.406361156067433</v>
       </c>
       <c r="H6" s="18">
         <f>'Passenger Vehicle Calculations'!I69</f>
-        <v>2224.0661798520518</v>
+        <v>90.685787530162571</v>
       </c>
       <c r="I6" s="18">
         <f>'Passenger Vehicle Calculations'!J69</f>
-        <v>2167.4924466149887</v>
+        <v>88.04445391277919</v>
       </c>
       <c r="J6" s="18">
         <f>'Passenger Vehicle Calculations'!K69</f>
-        <v>2112.6190346880921</v>
+        <v>85.480052342504052</v>
       </c>
       <c r="K6" s="18">
         <f>'Passenger Vehicle Calculations'!L69</f>
-        <v>2059.3856145068316</v>
+        <v>82.990342080101016</v>
       </c>
       <c r="L6" s="18">
         <f>'Passenger Vehicle Calculations'!M69</f>
-        <v>2006.7216198707158</v>
+        <v>80.573147650583522</v>
       </c>
       <c r="M6" s="18">
         <f>'Passenger Vehicle Calculations'!N69</f>
-        <v>1955.3640812230597</v>
+        <v>78.226356942314084</v>
       </c>
       <c r="N6" s="18">
         <f>'Passenger Vehicle Calculations'!O69</f>
@@ -12577,31 +12576,31 @@
       </c>
       <c r="G8" s="18">
         <f t="shared" si="0"/>
-        <v>3312.3286898445285</v>
+        <v>194.10400882122519</v>
       </c>
       <c r="H8" s="18">
         <f t="shared" si="0"/>
-        <v>2579.6280722494112</v>
+        <v>188.4504940011895</v>
       </c>
       <c r="I8" s="18">
         <f t="shared" si="0"/>
-        <v>2607.4715657030551</v>
+        <v>182.96164466134903</v>
       </c>
       <c r="J8" s="18">
         <f t="shared" si="0"/>
-        <v>2637.5199855509622</v>
+        <v>177.63266471975632</v>
       </c>
       <c r="K8" s="18">
         <f t="shared" si="0"/>
-        <v>2669.5709726607206</v>
+        <v>172.45889778617118</v>
       </c>
       <c r="L8" s="18">
         <f t="shared" si="0"/>
-        <v>2692.8330628056278</v>
+        <v>167.43582309337009</v>
       </c>
       <c r="M8" s="18">
         <f t="shared" si="0"/>
-        <v>2715.0603144269971</v>
+        <v>162.55905154696123</v>
       </c>
       <c r="N8" s="18">
         <f t="shared" si="0"/>
@@ -12812,85 +12811,78 @@
         <v>24444.57340361876</v>
       </c>
       <c r="G2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!F14*'Commercial Vehicles'!$B16</f>
-        <v>23732.59553749394</v>
+        <v>0</v>
       </c>
       <c r="H2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!G14*'Commercial Vehicles'!$B16</f>
-        <v>23041.354890770817</v>
+        <v>0</v>
       </c>
       <c r="I2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!H14*'Commercial Vehicles'!$B16</f>
-        <v>22370.247466767789</v>
+        <v>0</v>
       </c>
       <c r="J2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!I14*'Commercial Vehicles'!$B16</f>
-        <v>21718.686860939597</v>
+        <v>0</v>
       </c>
       <c r="K2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!J14*'Commercial Vehicles'!$B16</f>
-        <v>21086.103748485046</v>
+        <v>0</v>
       </c>
       <c r="L2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!K14*'Commercial Vehicles'!$B16</f>
-        <v>20471.945386878688</v>
+        <v>0</v>
       </c>
       <c r="M2" s="51">
-        <f>'Commercial Vehicles'!$B4*'Commercial Vehicles'!L14*'Commercial Vehicles'!$B16</f>
-        <v>19875.675132891927</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="51">
+        <v>0</v>
+      </c>
+      <c r="O2" s="51">
+        <v>0</v>
+      </c>
+      <c r="P2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="51">
+        <v>0</v>
+      </c>
+      <c r="R2" s="51">
+        <v>0</v>
+      </c>
+      <c r="S2" s="51">
+        <v>0</v>
+      </c>
+      <c r="T2" s="51">
+        <v>0</v>
+      </c>
+      <c r="U2" s="51">
+        <v>0</v>
+      </c>
+      <c r="V2" s="51">
+        <v>0</v>
+      </c>
+      <c r="W2" s="51">
+        <v>0</v>
+      </c>
+      <c r="X2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="51">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="51">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="51">
         <v>0</v>
       </c>
     </row>
@@ -13203,31 +13195,31 @@
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>23732.59553749394</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>23041.354890770817</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>22370.247466767789</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>21718.686860939597</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
-        <v>21086.103748485046</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
-        <v>20471.945386878688</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <f t="shared" si="0"/>
-        <v>19875.675132891927</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -13403,31 +13395,31 @@
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>23732.59553749394</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>23041.354890770817</v>
+        <v>0</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>22370.247466767789</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>21718.686860939597</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" si="1"/>
-        <v>21086.103748485046</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <f t="shared" si="1"/>
-        <v>20471.945386878688</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>19875.675132891927</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
